--- a/data/trending_integrated_20260922_14.xlsx
+++ b/data/trending_integrated_20260922_14.xlsx
@@ -584,7 +584,7 @@
         <v>94</v>
       </c>
       <c r="G2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52396608640</v>
+        <v>52402787340</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -676,7 +676,7 @@
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5452275269</v>
+        <v>5456299844</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -762,13 +762,13 @@
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>168014655800</v>
+        <v>170567078400</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13800</v>
+        <v>13650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+24.10%</t>
+          <t>'+22.75%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F5" t="n">
         <v>98</v>
       </c>
       <c r="G5" t="n">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>243067538865</v>
+        <v>248562930440</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>상한가 가능성 언급에도 불구하고 급락 및 사기꾼 언급 등 부정적 전망. 대미투자 관련 뉴스가 있으나 불확실성 존재.</t>
+          <t>급등 후 하한가 가능성에 대한 경고와 함께 투매 의견이 대립. 일부 속보 인용에도 불구하고, 기존 투자자에 대한 부정적 시각과 함께 급락 가능성이 제기됨.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['급락', '사기꾼', '대미투자']</t>
+          <t>['하한가', '개잡주', '투매']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111900</v>
+        <v>112800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.81%</t>
+          <t>'+10.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>298389681350</v>
+        <v>300735205750</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,27 +1027,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31300</v>
+        <v>31200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.49%</t>
+          <t>'+8.15%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="H7" t="n">
-        <v>52.47</v>
+        <v>52.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>25.79</v>
       </c>
       <c r="O7" t="n">
-        <v>157339017675</v>
+        <v>166016076075</v>
       </c>
       <c r="P7" t="n">
         <v>31400</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31600</v>
+        <v>31750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.40%</t>
+          <t>'+6.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.62</v>
       </c>
       <c r="E8" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F8" t="n">
         <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
         <v>11.3</v>
@@ -1162,7 +1162,7 @@
         <v>11.92</v>
       </c>
       <c r="O8" t="n">
-        <v>262702919975</v>
+        <v>265001573575</v>
       </c>
       <c r="P8" t="n">
         <v>75900</v>
@@ -1211,18 +1211,18 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18790</v>
+        <v>18870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+3.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.27</v>
       </c>
       <c r="E9" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F9" t="n">
         <v>83</v>
@@ -1254,7 +1254,7 @@
         <v>10.74</v>
       </c>
       <c r="O9" t="n">
-        <v>148252920790</v>
+        <v>149777595245</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6000</v>
+        <v>22100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+2.79%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.19</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5860</v>
+        <v>21500</v>
       </c>
       <c r="K10" t="n">
-        <v>6200</v>
+        <v>21200</v>
       </c>
       <c r="L10" t="n">
-        <v>6610</v>
+        <v>22900</v>
       </c>
       <c r="M10" t="n">
-        <v>5980</v>
+        <v>20850</v>
       </c>
       <c r="N10" t="n">
-        <v>0.19</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>67362806420</v>
+        <v>54185121475</v>
       </c>
       <c r="P10" t="n">
-        <v>13140</v>
+        <v>22900</v>
       </c>
       <c r="Q10" t="n">
-        <v>3725</v>
+        <v>9900</v>
       </c>
       <c r="R10" t="n">
-        <v>-259000</v>
+        <v>79000</v>
       </c>
       <c r="S10" t="n">
-        <v>34000</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>비트코인 급등에 따른 가상화폐 테마 상승 기대감. 업비트 상장 및 공매도 관련 언급.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['비트코인', '가상화폐', '공매도']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>212500</v>
+        <v>6010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.16%</t>
+          <t>'+2.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>342</v>
+        <v>161</v>
       </c>
       <c r="H11" t="n">
-        <v>75.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>208000</v>
+        <v>5860</v>
       </c>
       <c r="K11" t="n">
-        <v>215000</v>
+        <v>6200</v>
       </c>
       <c r="L11" t="n">
-        <v>216000</v>
+        <v>6610</v>
       </c>
       <c r="M11" t="n">
-        <v>211000</v>
+        <v>5980</v>
       </c>
       <c r="N11" t="n">
-        <v>75.44</v>
+        <v>0.19</v>
       </c>
       <c r="O11" t="n">
-        <v>784476533500</v>
+        <v>67828106755</v>
       </c>
       <c r="P11" t="n">
-        <v>243500</v>
+        <v>13140</v>
       </c>
       <c r="Q11" t="n">
-        <v>64700</v>
+        <v>3725</v>
       </c>
       <c r="R11" t="n">
-        <v>-683000</v>
+        <v>-259000</v>
       </c>
       <c r="S11" t="n">
-        <v>-90000</v>
+        <v>34000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>비트코인 급등에 따른 가상화폐 테마 상승 기대감. 업비트 상장 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['비트코인', '가상화폐', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>277750</v>
+        <v>213000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.37%</t>
+          <t>'+2.40%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
-        <v>475</v>
+        <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>2006</v>
+        <v>344</v>
       </c>
       <c r="H12" t="n">
-        <v>46.56</v>
+        <v>75.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>274000</v>
+        <v>208000</v>
       </c>
       <c r="K12" t="n">
-        <v>283000</v>
+        <v>215000</v>
       </c>
       <c r="L12" t="n">
-        <v>283500</v>
+        <v>216000</v>
       </c>
       <c r="M12" t="n">
-        <v>276500</v>
+        <v>211000</v>
       </c>
       <c r="N12" t="n">
-        <v>46.46</v>
+        <v>75.44</v>
       </c>
       <c r="O12" t="n">
-        <v>3307656925500</v>
+        <v>803466492250</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>243500</v>
       </c>
       <c r="Q12" t="n">
-        <v>81100</v>
+        <v>64700</v>
       </c>
       <c r="R12" t="n">
-        <v>550000</v>
+        <v>-683000</v>
       </c>
       <c r="S12" t="n">
-        <v>307000</v>
+        <v>-90000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 낙관론에 따른 주가 상승 기대감 존재. 3분기 배당 기준일 부근 분위기 긍정 전망.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI', '배당금', '주가']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13130</v>
+        <v>86700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.31%</t>
+          <t>'+1.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>402</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>213</v>
       </c>
       <c r="G13" t="n">
-        <v>365</v>
+        <v>1460</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>23.05</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12960</v>
+        <v>85300</v>
       </c>
       <c r="K13" t="n">
-        <v>13500</v>
+        <v>87000</v>
       </c>
       <c r="L13" t="n">
-        <v>14190</v>
+        <v>88100</v>
       </c>
       <c r="M13" t="n">
-        <v>13120</v>
+        <v>85200</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>23.12</v>
       </c>
       <c r="O13" t="n">
-        <v>22184457145</v>
+        <v>209498572750</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-46000</v>
+        <v>-240000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>미국 투자 유치 관련 속보 및 공급 계약 체결 가능성에 대한 기대감 고조. SMR 사업 추진 확정 뉴스 인용으로 긍정적 전망이 형성됨. 공매도 관련 언급 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['SMR', '대미투자', '공급계약']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86400</v>
+        <v>13160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.29%</t>
+          <t>'+1.54%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>399</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
-        <v>213</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>1455</v>
+        <v>366</v>
       </c>
       <c r="H14" t="n">
-        <v>23.05</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,183 +1699,183 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>85300</v>
+        <v>12960</v>
       </c>
       <c r="K14" t="n">
-        <v>87000</v>
+        <v>13500</v>
       </c>
       <c r="L14" t="n">
-        <v>88100</v>
+        <v>14190</v>
       </c>
       <c r="M14" t="n">
-        <v>85200</v>
+        <v>13120</v>
       </c>
       <c r="N14" t="n">
-        <v>23.12</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>205258675450</v>
+        <v>22353840815</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-240000</v>
+        <v>-46000</v>
       </c>
       <c r="S14" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 투자 관련 공급 계약 체결 및 SMR 추진 확정 뉴스 기반 기대감. 공매도에 대한 부정적 언급.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공급계약', 'SMR', '공매도']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21750</v>
+        <v>323000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.16%</t>
+          <t>'+1.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.05</v>
+        <v>-0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
-        <v>226</v>
+        <v>307</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2</v>
+        <v>3.22</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>21500</v>
+        <v>318500</v>
       </c>
       <c r="K15" t="n">
-        <v>21200</v>
+        <v>333000</v>
       </c>
       <c r="L15" t="n">
-        <v>22900</v>
+        <v>349500</v>
       </c>
       <c r="M15" t="n">
-        <v>20850</v>
+        <v>320000</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>3.62</v>
       </c>
       <c r="O15" t="n">
-        <v>52089945275</v>
+        <v>121596322000</v>
       </c>
       <c r="P15" t="n">
-        <v>22900</v>
+        <v>635000</v>
       </c>
       <c r="Q15" t="n">
-        <v>9900</v>
+        <v>52600</v>
       </c>
       <c r="R15" t="n">
-        <v>79000</v>
+        <v>-7000</v>
       </c>
       <c r="S15" t="n">
-        <v>-8000</v>
+        <v>5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>텍사스 가스복합발전 프로젝트 관련 수혜 기대감과 함께 신고가 경신 및 50만원 돌파 전망 제시. 구리 가격 상승 및 성장 동력에 대한 긍정적 언급 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['신고가', '성장동력', '가스복합발전']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>322000</v>
+        <v>277500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.10%</t>
+          <t>'+1.28%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>129</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>478</v>
       </c>
       <c r="G16" t="n">
-        <v>302</v>
+        <v>1947</v>
       </c>
       <c r="H16" t="n">
-        <v>3.22</v>
+        <v>46.56</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>318500</v>
+        <v>274000</v>
       </c>
       <c r="K16" t="n">
-        <v>333000</v>
+        <v>283000</v>
       </c>
       <c r="L16" t="n">
-        <v>349500</v>
+        <v>283500</v>
       </c>
       <c r="M16" t="n">
-        <v>320000</v>
+        <v>276500</v>
       </c>
       <c r="N16" t="n">
-        <v>3.62</v>
+        <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>120563187250</v>
+        <v>3413431999750</v>
       </c>
       <c r="P16" t="n">
-        <v>635000</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>52600</v>
+        <v>81100</v>
       </c>
       <c r="R16" t="n">
-        <v>-7000</v>
+        <v>550000</v>
       </c>
       <c r="S16" t="n">
-        <v>5000</v>
+        <v>307000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 및 40만원 이상 상승 기대감 형성. 테마주 관련 언급.</t>
+          <t>시장 기대감과 정치적 언급이 혼재된 가운데, 개인 투자자들의 기대감이 나타남. 단기 주가 상승 및 배당 증액에 대한 희망이 존재하나, 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['신고가', '테마주', '상승']</t>
+          <t>['특별배당', '주가전망', '배당기준일']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13640</v>
+        <v>6390</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.74%</t>
+          <t>'+1.27%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.34</v>
+        <v>-0.09</v>
       </c>
       <c r="E17" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G17" t="n">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="H17" t="n">
-        <v>3.34</v>
+        <v>4.86</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13540</v>
+        <v>6310</v>
       </c>
       <c r="K17" t="n">
-        <v>13870</v>
+        <v>6460</v>
       </c>
       <c r="L17" t="n">
-        <v>14650</v>
+        <v>7090</v>
       </c>
       <c r="M17" t="n">
-        <v>13610</v>
+        <v>6330</v>
       </c>
       <c r="N17" t="n">
-        <v>3.68</v>
+        <v>4.95</v>
       </c>
       <c r="O17" t="n">
-        <v>96267418995</v>
+        <v>53767920840</v>
       </c>
       <c r="P17" t="n">
-        <v>20300</v>
+        <v>11760</v>
       </c>
       <c r="Q17" t="n">
-        <v>2885</v>
+        <v>1620</v>
       </c>
       <c r="R17" t="n">
-        <v>8000</v>
+        <v>-74000</v>
       </c>
       <c r="S17" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6355</v>
+        <v>13700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.71%</t>
+          <t>'+1.18%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.09</v>
+        <v>-0.34</v>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
-        <v>4.86</v>
+        <v>3.34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6310</v>
+        <v>13540</v>
       </c>
       <c r="K18" t="n">
-        <v>6460</v>
+        <v>13870</v>
       </c>
       <c r="L18" t="n">
-        <v>7090</v>
+        <v>14650</v>
       </c>
       <c r="M18" t="n">
-        <v>6330</v>
+        <v>13610</v>
       </c>
       <c r="N18" t="n">
-        <v>4.95</v>
+        <v>3.68</v>
       </c>
       <c r="O18" t="n">
-        <v>53501118305</v>
+        <v>96783911145</v>
       </c>
       <c r="P18" t="n">
-        <v>11760</v>
+        <v>20300</v>
       </c>
       <c r="Q18" t="n">
-        <v>1620</v>
+        <v>2885</v>
       </c>
       <c r="R18" t="n">
-        <v>-74000</v>
+        <v>8000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13420</v>
+        <v>13450</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.15%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>61</v>
       </c>
       <c r="G19" t="n">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="H19" t="n">
         <v>5.02</v>
@@ -2174,7 +2174,7 @@
         <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>64471950550</v>
+        <v>65118841500</v>
       </c>
       <c r="P19" t="n">
         <v>30200</v>
@@ -2219,83 +2219,83 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1867500</v>
+        <v>17770</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.03%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.06</v>
+        <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>188</v>
       </c>
       <c r="F20" t="n">
-        <v>476</v>
+        <v>105</v>
       </c>
       <c r="G20" t="n">
-        <v>1713</v>
+        <v>793</v>
       </c>
       <c r="H20" t="n">
-        <v>50.17</v>
+        <v>6.22</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1868000</v>
+        <v>17720</v>
       </c>
       <c r="K20" t="n">
-        <v>1909000</v>
+        <v>18230</v>
       </c>
       <c r="L20" t="n">
-        <v>1935000</v>
+        <v>18750</v>
       </c>
       <c r="M20" t="n">
-        <v>1860000</v>
+        <v>17500</v>
       </c>
       <c r="N20" t="n">
-        <v>50.23</v>
+        <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>4000331806000</v>
+        <v>158455095440</v>
       </c>
       <c r="P20" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>333000</v>
+        <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>44000</v>
+        <v>-494000</v>
       </c>
       <c r="S20" t="n">
-        <v>31000</v>
+        <v>14000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 부정적 언급 및 매물대, 외인/기관 동향 분석. 단타 세력 비판.</t>
+          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대감. 실적 및 추세 긍정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['매물대', '외인', '주가']</t>
+          <t>['광통신', '실적', '추세']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17670</v>
+        <v>10550</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.68</v>
+        <v>1.01</v>
       </c>
       <c r="E21" t="n">
-        <v>186</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>791</v>
+        <v>193</v>
       </c>
       <c r="H21" t="n">
-        <v>6.22</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,91 +2343,91 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17720</v>
+        <v>10550</v>
       </c>
       <c r="K21" t="n">
-        <v>18230</v>
+        <v>10730</v>
       </c>
       <c r="L21" t="n">
-        <v>18750</v>
+        <v>11160</v>
       </c>
       <c r="M21" t="n">
-        <v>17500</v>
+        <v>10300</v>
       </c>
       <c r="N21" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="O21" t="n">
-        <v>156694110810</v>
+        <v>141056363965</v>
       </c>
       <c r="P21" t="n">
-        <v>31500</v>
+        <v>11640</v>
       </c>
       <c r="Q21" t="n">
-        <v>1272</v>
+        <v>3735</v>
       </c>
       <c r="R21" t="n">
-        <v>-494000</v>
+        <v>215000</v>
       </c>
       <c r="S21" t="n">
-        <v>14000</v>
+        <v>-478000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대감. 실적 및 추세 긍정적 전망.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['광통신', '실적', '추세']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8470</v>
+        <v>1861500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E22" t="n">
-        <v>114</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>48</v>
+        <v>484</v>
       </c>
       <c r="G22" t="n">
-        <v>387</v>
+        <v>1788</v>
       </c>
       <c r="H22" t="n">
-        <v>26.58</v>
+        <v>50.17</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,130 +2435,130 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>8520</v>
+        <v>1868000</v>
       </c>
       <c r="K22" t="n">
-        <v>8620</v>
+        <v>1909000</v>
       </c>
       <c r="L22" t="n">
-        <v>8650</v>
+        <v>1935000</v>
       </c>
       <c r="M22" t="n">
-        <v>8410</v>
+        <v>1860000</v>
       </c>
       <c r="N22" t="n">
-        <v>26.57</v>
+        <v>50.23</v>
       </c>
       <c r="O22" t="n">
-        <v>19173692350</v>
+        <v>4149793605000</v>
       </c>
       <c r="P22" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q22" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R22" t="n">
-        <v>-436000</v>
+        <v>44000</v>
       </c>
       <c r="S22" t="n">
-        <v>72000</v>
+        <v>31000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>대미 투자 관련 언급이 다수 확인되며, SMR 추진 및 가스터빈 기술에 대한 기대감 존재. 주가 상승에 대한 기대와 우려가 공존.</t>
+          <t>국내 증시 전반의 불안감 속에서 SK하이닉스 주가 하락 및 기관/연기금 매도에 대한 불만이 표출됨. 외인 매수세에도 불구하고 주가 부진에 대한 부정적 전망이 우세함.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['SMR', '대미 투자', '가스터빈']</t>
+          <t>['연기금', '매물대', '주가부진']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10420</v>
+        <v>8480</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-1.23%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.01</v>
+        <v>0.01</v>
       </c>
       <c r="E23" t="n">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G23" t="n">
-        <v>191</v>
+        <v>392</v>
       </c>
       <c r="H23" t="n">
-        <v>9.609999999999999</v>
+        <v>26.58</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>10550</v>
+        <v>8520</v>
       </c>
       <c r="K23" t="n">
-        <v>10730</v>
+        <v>8620</v>
       </c>
       <c r="L23" t="n">
-        <v>11160</v>
+        <v>8650</v>
       </c>
       <c r="M23" t="n">
-        <v>10300</v>
+        <v>8410</v>
       </c>
       <c r="N23" t="n">
-        <v>8.6</v>
+        <v>26.57</v>
       </c>
       <c r="O23" t="n">
-        <v>139193101730</v>
+        <v>19629146625</v>
       </c>
       <c r="P23" t="n">
-        <v>11640</v>
+        <v>17950</v>
       </c>
       <c r="Q23" t="n">
-        <v>3735</v>
+        <v>8120</v>
       </c>
       <c r="R23" t="n">
-        <v>215000</v>
+        <v>-436000</v>
       </c>
       <c r="S23" t="n">
-        <v>-478000</v>
+        <v>72000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>대미 투자 관련 언급이 다수 확인되며, SMR 추진 및 가스터빈 기술에 대한 기대감 존재. 주가 상승에 대한 기대와 우려가 공존.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['SMR', '대미 투자', '가스터빈']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23800</v>
+        <v>23950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.74%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1.41</v>
       </c>
       <c r="E24" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" t="n">
         <v>62</v>
       </c>
       <c r="G24" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H24" t="n">
         <v>1.76</v>
@@ -2634,7 +2634,7 @@
         <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>106131864775</v>
+        <v>106959606825</v>
       </c>
       <c r="P24" t="n">
         <v>39350</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3770</v>
+        <v>3760</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-7.03%</t>
+          <t>'-7.27%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0.63</v>
       </c>
       <c r="E25" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G25" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="H25" t="n">
         <v>0.96</v>
@@ -2726,7 +2726,7 @@
         <v>0.33</v>
       </c>
       <c r="O25" t="n">
-        <v>12377704575</v>
+        <v>12575488290</v>
       </c>
       <c r="P25" t="n">
         <v>6480</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10220</v>
+        <v>10250</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-7.59%</t>
+          <t>'-7.32%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>-0.4</v>
       </c>
       <c r="E26" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G26" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H26" t="n">
         <v>17.89</v>
@@ -2818,7 +2818,7 @@
         <v>18.29</v>
       </c>
       <c r="O26" t="n">
-        <v>39909741535</v>
+        <v>40675052155</v>
       </c>
       <c r="P26" t="n">
         <v>22450</v>

--- a/data/trending_integrated_20260922_14.xlsx
+++ b/data/trending_integrated_20260922_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G2" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52402787340</v>
+        <v>52404861940</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스 기반으로 주가 급등. AI 반도체 파트너십 기대.</t>
+          <t>노타의 국산 NPU 기반 휴머노이드 개발 착수 소식에 따른 긍정적 전망. 기술력에 대한 높은 평가와 함께 주가 상승에 대한 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', 'AI']</t>
+          <t>['휴머노이드', 'NPU', '기술력']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5456299844</v>
+        <v>5460811984</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65200</v>
+        <v>64700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+24.67%</t>
+          <t>'+23.71%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
         <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>170567078400</v>
+        <v>172621893100</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13650</v>
+        <v>13430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+22.75%</t>
+          <t>'+20.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G5" t="n">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>248562930440</v>
+        <v>253196201805</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>급등 후 하한가 가능성에 대한 경고와 함께 투매 의견이 대립. 일부 속보 인용에도 불구하고, 기존 투자자에 대한 부정적 시각과 함께 급락 가능성이 제기됨.</t>
+          <t>삼미금속 주가 하락에 대한 부정적 전망과 경고. 일부 투자자들의 매수 행태를 이해하지 못하겠다는 의견과 함께 하한가 가능성을 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['하한가', '개잡주', '투매']</t>
+          <t>['하한가', '주가', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112800</v>
+        <v>111300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.70%</t>
+          <t>'+9.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
         <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>300735205750</v>
+        <v>304917227100</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,27 +1027,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31200</v>
+        <v>30950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.15%</t>
+          <t>'+7.28%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="H7" t="n">
-        <v>52.5</v>
+        <v>52.51</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>25.79</v>
       </c>
       <c r="O7" t="n">
-        <v>166016076075</v>
+        <v>171083531025</v>
       </c>
       <c r="P7" t="n">
         <v>31400</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31750</v>
+        <v>31550</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.90%</t>
+          <t>'+6.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.62</v>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="H8" t="n">
         <v>11.3</v>
@@ -1162,7 +1162,7 @@
         <v>11.92</v>
       </c>
       <c r="O8" t="n">
-        <v>265001573575</v>
+        <v>266847445075</v>
       </c>
       <c r="P8" t="n">
         <v>75900</v>
@@ -1207,184 +1207,184 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18870</v>
+        <v>22600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.17%</t>
+          <t>'+5.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.27</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="F9" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>741</v>
+        <v>242</v>
       </c>
       <c r="H9" t="n">
-        <v>10.47</v>
+        <v>1.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18290</v>
+        <v>21500</v>
       </c>
       <c r="K9" t="n">
-        <v>18830</v>
+        <v>21200</v>
       </c>
       <c r="L9" t="n">
-        <v>19540</v>
+        <v>23200</v>
       </c>
       <c r="M9" t="n">
-        <v>18540</v>
+        <v>20850</v>
       </c>
       <c r="N9" t="n">
-        <v>10.74</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>149777595245</v>
+        <v>67850598475</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>23200</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>9900</v>
       </c>
       <c r="R9" t="n">
-        <v>146000</v>
+        <v>79000</v>
       </c>
       <c r="S9" t="n">
-        <v>41000</v>
+        <v>-8000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>공매도 관련 내용 언급 및 감사원 신고 완료 주장. 미국 증시 폭등과 함께 상승 기대.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '감사원', '상승']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22100</v>
+        <v>18740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.79%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G10" t="n">
-        <v>231</v>
+        <v>746</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2</v>
+        <v>10.47</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>21500</v>
+        <v>18290</v>
       </c>
       <c r="K10" t="n">
-        <v>21200</v>
+        <v>18830</v>
       </c>
       <c r="L10" t="n">
-        <v>22900</v>
+        <v>19540</v>
       </c>
       <c r="M10" t="n">
-        <v>20850</v>
+        <v>18540</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>54185121475</v>
+        <v>152533381585</v>
       </c>
       <c r="P10" t="n">
-        <v>22900</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>9900</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>79000</v>
+        <v>146000</v>
       </c>
       <c r="S10" t="n">
-        <v>-8000</v>
+        <v>41000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>공매도 관련 내용 언급 및 감사원 신고 완료 주장. 미국 증시 폭등과 함께 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['공매도', '감사원', '상승']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6010</v>
+        <v>5970</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.56%</t>
+          <t>'+1.88%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>6610</v>
       </c>
       <c r="M11" t="n">
-        <v>5980</v>
+        <v>5950</v>
       </c>
       <c r="N11" t="n">
         <v>0.19</v>
       </c>
       <c r="O11" t="n">
-        <v>67828106755</v>
+        <v>68346548885</v>
       </c>
       <c r="P11" t="n">
         <v>13140</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>213000</v>
+        <v>211500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.40%</t>
+          <t>'+1.68%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="H12" t="n">
         <v>75.5</v>
@@ -1530,7 +1530,7 @@
         <v>75.44</v>
       </c>
       <c r="O12" t="n">
-        <v>803466492250</v>
+        <v>824691961000</v>
       </c>
       <c r="P12" t="n">
         <v>243500</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>86700</v>
+        <v>13140</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.64%</t>
+          <t>'+1.39%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>402</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>213</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>1460</v>
+        <v>377</v>
       </c>
       <c r="H13" t="n">
-        <v>23.05</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>85300</v>
+        <v>12960</v>
       </c>
       <c r="K13" t="n">
-        <v>87000</v>
+        <v>13500</v>
       </c>
       <c r="L13" t="n">
-        <v>88100</v>
+        <v>14190</v>
       </c>
       <c r="M13" t="n">
-        <v>85200</v>
+        <v>13120</v>
       </c>
       <c r="N13" t="n">
-        <v>23.12</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>209498572750</v>
+        <v>22557596260</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-240000</v>
+        <v>-46000</v>
       </c>
       <c r="S13" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 투자 유치 관련 속보 및 공급 계약 체결 가능성에 대한 기대감 고조. SMR 사업 추진 확정 뉴스 인용으로 긍정적 전망이 형성됨. 공매도 관련 언급 존재.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['SMR', '대미투자', '공급계약']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13160</v>
+        <v>86200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.54%</t>
+          <t>'+1.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>412</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="G14" t="n">
-        <v>366</v>
+        <v>1501</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>23.05</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,139 +1699,139 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>12960</v>
+        <v>85300</v>
       </c>
       <c r="K14" t="n">
-        <v>13500</v>
+        <v>87000</v>
       </c>
       <c r="L14" t="n">
-        <v>14190</v>
+        <v>88100</v>
       </c>
       <c r="M14" t="n">
-        <v>13120</v>
+        <v>85200</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>23.12</v>
       </c>
       <c r="O14" t="n">
-        <v>22353840815</v>
+        <v>214007176650</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-46000</v>
+        <v>-240000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>두산에너빌리티의 대미 투자 및 SMR 추진 확정 소식으로 인한 긍정적 전망. 공급 계약 체결에 대한 축하 메시지와 함께 주가 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['대미투자', 'SMR', '공급계약']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>323000</v>
+        <v>6370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.41%</t>
+          <t>'+0.95%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.4</v>
+        <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="F15" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="H15" t="n">
-        <v>3.22</v>
+        <v>4.86</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>318500</v>
+        <v>6310</v>
       </c>
       <c r="K15" t="n">
-        <v>333000</v>
+        <v>6460</v>
       </c>
       <c r="L15" t="n">
-        <v>349500</v>
+        <v>7090</v>
       </c>
       <c r="M15" t="n">
-        <v>320000</v>
+        <v>6330</v>
       </c>
       <c r="N15" t="n">
-        <v>3.62</v>
+        <v>4.95</v>
       </c>
       <c r="O15" t="n">
-        <v>121596322000</v>
+        <v>54014395300</v>
       </c>
       <c r="P15" t="n">
-        <v>635000</v>
+        <v>11760</v>
       </c>
       <c r="Q15" t="n">
-        <v>52600</v>
+        <v>1620</v>
       </c>
       <c r="R15" t="n">
-        <v>-7000</v>
+        <v>-74000</v>
       </c>
       <c r="S15" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>텍사스 가스복합발전 프로젝트 관련 수혜 기대감과 함께 신고가 경신 및 50만원 돌파 전망 제시. 구리 가격 상승 및 성장 동력에 대한 긍정적 언급 존재.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['신고가', '성장동력', '가스복합발전']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>277500</v>
+        <v>276000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.28%</t>
+          <t>'+0.73%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G16" t="n">
-        <v>1947</v>
+        <v>1861</v>
       </c>
       <c r="H16" t="n">
         <v>46.56</v>
@@ -1892,13 +1892,13 @@
         <v>283500</v>
       </c>
       <c r="M16" t="n">
-        <v>276500</v>
+        <v>275500</v>
       </c>
       <c r="N16" t="n">
         <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>3413431999750</v>
+        <v>3557264373250</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>시장 기대감과 정치적 언급이 혼재된 가운데, 개인 투자자들의 기대감이 나타남. 단기 주가 상승 및 배당 증액에 대한 희망이 존재하나, 구체적인 근거는 부족함.</t>
+          <t>삼성전자에 대한 긍정적 기대감과 함께 주가 상승 전망 언급. 다만, 일부 부정적 의견과 함께 물량 출회에 대한 우려도 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['특별배당', '주가전망', '배당기준일']</t>
+          <t>['특별배당', '실적', '주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,79 +1943,79 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6390</v>
+        <v>320500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.27%</t>
+          <t>'+0.63%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.09</v>
+        <v>-0.4</v>
       </c>
       <c r="E17" t="n">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
-        <v>182</v>
+        <v>312</v>
       </c>
       <c r="H17" t="n">
-        <v>4.86</v>
+        <v>3.22</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6310</v>
+        <v>318500</v>
       </c>
       <c r="K17" t="n">
-        <v>6460</v>
+        <v>333000</v>
       </c>
       <c r="L17" t="n">
-        <v>7090</v>
+        <v>349500</v>
       </c>
       <c r="M17" t="n">
-        <v>6330</v>
+        <v>320000</v>
       </c>
       <c r="N17" t="n">
-        <v>4.95</v>
+        <v>3.62</v>
       </c>
       <c r="O17" t="n">
-        <v>53767920840</v>
+        <v>122914990500</v>
       </c>
       <c r="P17" t="n">
-        <v>11760</v>
+        <v>635000</v>
       </c>
       <c r="Q17" t="n">
-        <v>1620</v>
+        <v>52600</v>
       </c>
       <c r="R17" t="n">
-        <v>-74000</v>
+        <v>-7000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>가온전선 주가 상승에 대한 긍정적 전망. 52주 신고가 돌파 기대감과 함께 40만원, 50만원 목표가를 제시하며 매수세를 독려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['신고가', '목표가', '성장동력']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13700</v>
+        <v>13600</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.18%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.34</v>
       </c>
       <c r="E18" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="H18" t="n">
         <v>3.34</v>
@@ -2076,13 +2076,13 @@
         <v>14650</v>
       </c>
       <c r="M18" t="n">
-        <v>13610</v>
+        <v>13590</v>
       </c>
       <c r="N18" t="n">
         <v>3.68</v>
       </c>
       <c r="O18" t="n">
-        <v>96783911145</v>
+        <v>97589239195</v>
       </c>
       <c r="P18" t="n">
         <v>20300</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13450</v>
+        <v>13360</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'-0.30%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.48</v>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F19" t="n">
         <v>61</v>
       </c>
       <c r="G19" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="H19" t="n">
         <v>5.02</v>
@@ -2174,7 +2174,7 @@
         <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>65118841500</v>
+        <v>66741781170</v>
       </c>
       <c r="P19" t="n">
         <v>30200</v>
@@ -2219,123 +2219,123 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17770</v>
+        <v>8480</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.68</v>
+        <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>188</v>
+        <v>117</v>
       </c>
       <c r="F20" t="n">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="G20" t="n">
-        <v>793</v>
+        <v>401</v>
       </c>
       <c r="H20" t="n">
-        <v>6.22</v>
+        <v>26.58</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>17720</v>
+        <v>8520</v>
       </c>
       <c r="K20" t="n">
-        <v>18230</v>
+        <v>8620</v>
       </c>
       <c r="L20" t="n">
-        <v>18750</v>
+        <v>8650</v>
       </c>
       <c r="M20" t="n">
-        <v>17500</v>
+        <v>8410</v>
       </c>
       <c r="N20" t="n">
-        <v>7.9</v>
+        <v>26.57</v>
       </c>
       <c r="O20" t="n">
-        <v>158455095440</v>
+        <v>20027455225</v>
       </c>
       <c r="P20" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q20" t="n">
-        <v>1272</v>
+        <v>8120</v>
       </c>
       <c r="R20" t="n">
-        <v>-494000</v>
+        <v>-436000</v>
       </c>
       <c r="S20" t="n">
-        <v>14000</v>
+        <v>72000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대감. 실적 및 추세 긍정적 전망.</t>
+          <t>대미 투자 관련 언급이 다수 확인되며, SMR 추진 및 가스터빈 기술에 대한 기대감 존재. 주가 상승에 대한 기대와 우려가 공존.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '실적', '추세']</t>
+          <t>['SMR', '대미 투자', '가스터빈']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10550</v>
+        <v>17620</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="G21" t="n">
-        <v>193</v>
+        <v>799</v>
       </c>
       <c r="H21" t="n">
-        <v>9.609999999999999</v>
+        <v>6.22</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,183 +2343,183 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10550</v>
+        <v>17720</v>
       </c>
       <c r="K21" t="n">
-        <v>10730</v>
+        <v>18230</v>
       </c>
       <c r="L21" t="n">
-        <v>11160</v>
+        <v>18750</v>
       </c>
       <c r="M21" t="n">
-        <v>10300</v>
+        <v>17500</v>
       </c>
       <c r="N21" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="O21" t="n">
-        <v>141056363965</v>
+        <v>161213216990</v>
       </c>
       <c r="P21" t="n">
-        <v>11640</v>
+        <v>31500</v>
       </c>
       <c r="Q21" t="n">
-        <v>3735</v>
+        <v>1272</v>
       </c>
       <c r="R21" t="n">
-        <v>215000</v>
+        <v>-494000</v>
       </c>
       <c r="S21" t="n">
-        <v>-478000</v>
+        <v>14000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대감. 실적 및 추세 긍정적 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['광통신', '실적', '추세']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1861500</v>
+        <v>10480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.66%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.06</v>
+        <v>1.01</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>67</v>
       </c>
       <c r="F22" t="n">
-        <v>484</v>
+        <v>42</v>
       </c>
       <c r="G22" t="n">
-        <v>1788</v>
+        <v>193</v>
       </c>
       <c r="H22" t="n">
-        <v>50.17</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1868000</v>
+        <v>10550</v>
       </c>
       <c r="K22" t="n">
-        <v>1909000</v>
+        <v>10730</v>
       </c>
       <c r="L22" t="n">
-        <v>1935000</v>
+        <v>11160</v>
       </c>
       <c r="M22" t="n">
-        <v>1860000</v>
+        <v>10300</v>
       </c>
       <c r="N22" t="n">
-        <v>50.23</v>
+        <v>8.6</v>
       </c>
       <c r="O22" t="n">
-        <v>4149793605000</v>
+        <v>142705857420</v>
       </c>
       <c r="P22" t="n">
-        <v>2987000</v>
+        <v>11640</v>
       </c>
       <c r="Q22" t="n">
-        <v>333000</v>
+        <v>3735</v>
       </c>
       <c r="R22" t="n">
-        <v>44000</v>
+        <v>215000</v>
       </c>
       <c r="S22" t="n">
-        <v>31000</v>
+        <v>-478000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>국내 증시 전반의 불안감 속에서 SK하이닉스 주가 하락 및 기관/연기금 매도에 대한 불만이 표출됨. 외인 매수세에도 불구하고 주가 부진에 대한 부정적 전망이 우세함.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['연기금', '매물대', '주가부진']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8480</v>
+        <v>1849000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-1.02%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E23" t="n">
-        <v>116</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>481</v>
       </c>
       <c r="G23" t="n">
-        <v>392</v>
+        <v>1658</v>
       </c>
       <c r="H23" t="n">
-        <v>26.58</v>
+        <v>50.17</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,60 +2527,60 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>8520</v>
+        <v>1868000</v>
       </c>
       <c r="K23" t="n">
-        <v>8620</v>
+        <v>1909000</v>
       </c>
       <c r="L23" t="n">
-        <v>8650</v>
+        <v>1935000</v>
       </c>
       <c r="M23" t="n">
-        <v>8410</v>
+        <v>1846000</v>
       </c>
       <c r="N23" t="n">
-        <v>26.57</v>
+        <v>50.23</v>
       </c>
       <c r="O23" t="n">
-        <v>19629146625</v>
+        <v>4372674227500</v>
       </c>
       <c r="P23" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R23" t="n">
-        <v>-436000</v>
+        <v>44000</v>
       </c>
       <c r="S23" t="n">
-        <v>72000</v>
+        <v>31000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>대미 투자 관련 언급이 다수 확인되며, SMR 추진 및 가스터빈 기술에 대한 기대감 존재. 주가 상승에 대한 기대와 우려가 공존.</t>
+          <t>SK하이닉스 주가 하락에 대한 불만과 부정적 전망. 연기금 매도와 기관 수급에 대한 비판, 그리고 장중 주가 변동성에 대한 우려가 나타남.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['SMR', '대미 투자', '가스터빈']</t>
+          <t>['연기금', '주가', '기관']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
         <v>1.41</v>
       </c>
       <c r="E24" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" t="n">
         <v>62</v>
@@ -2634,7 +2634,7 @@
         <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>106959606825</v>
+        <v>107906339825</v>
       </c>
       <c r="P24" t="n">
         <v>39350</v>
@@ -2679,70 +2679,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3760</v>
+        <v>10220</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-7.27%</t>
+          <t>'-7.59%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.63</v>
+        <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="F25" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G25" t="n">
-        <v>327</v>
+        <v>261</v>
       </c>
       <c r="H25" t="n">
-        <v>0.96</v>
+        <v>17.89</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>4055</v>
+        <v>11060</v>
       </c>
       <c r="K25" t="n">
-        <v>4080</v>
+        <v>10570</v>
       </c>
       <c r="L25" t="n">
-        <v>4080</v>
+        <v>10815</v>
       </c>
       <c r="M25" t="n">
-        <v>3735</v>
+        <v>10060</v>
       </c>
       <c r="N25" t="n">
-        <v>0.33</v>
+        <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>12575488290</v>
+        <v>41110837205</v>
       </c>
       <c r="P25" t="n">
-        <v>6480</v>
+        <v>22450</v>
       </c>
       <c r="Q25" t="n">
-        <v>1738</v>
+        <v>1760</v>
       </c>
       <c r="R25" t="n">
-        <v>-28000</v>
+        <v>-11000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>텐베거 기대감 속 급락 및 신규 매수 개미 몰살 우려. 차트상 말아 올리는 패턴 기대.</t>
+          <t>투자경고 종목 지정 및 단주치기 등 거래 행태에 대한 부정적 인식. 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['텐베거', '차트분석', '급락']</t>
+          <t>['투자경고', '단주치기', '주가']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,77 +2764,77 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10250</v>
+        <v>3720</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-7.32%</t>
+          <t>'-8.26%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.4</v>
+        <v>0.63</v>
       </c>
       <c r="E26" t="n">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="F26" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G26" t="n">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="H26" t="n">
-        <v>17.89</v>
+        <v>0.96</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>11060</v>
+        <v>4055</v>
       </c>
       <c r="K26" t="n">
-        <v>10570</v>
+        <v>4080</v>
       </c>
       <c r="L26" t="n">
-        <v>10815</v>
+        <v>4080</v>
       </c>
       <c r="M26" t="n">
-        <v>10060</v>
+        <v>3720</v>
       </c>
       <c r="N26" t="n">
-        <v>18.29</v>
+        <v>0.33</v>
       </c>
       <c r="O26" t="n">
-        <v>40675052155</v>
+        <v>12859656295</v>
       </c>
       <c r="P26" t="n">
-        <v>22450</v>
+        <v>6480</v>
       </c>
       <c r="Q26" t="n">
-        <v>1760</v>
+        <v>1738</v>
       </c>
       <c r="R26" t="n">
-        <v>-11000</v>
+        <v>-28000</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 및 단주치기 등 거래 행태에 대한 부정적 인식. 주가 하락 우려.</t>
+          <t>텐베거 기대감 속 급락 및 신규 매수 개미 몰살 우려. 차트상 말아 올리는 패턴 기대.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,11 +2843,11 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['투자경고', '단주치기', '주가']</t>
+          <t>['텐베거', '차트분석', '급락']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>201490</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260922_14.xlsx
+++ b/data/trending_integrated_20260922_14.xlsx
@@ -584,7 +584,7 @@
         <v>93</v>
       </c>
       <c r="G2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52404861940</v>
+        <v>52415911440</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>노타의 국산 NPU 기반 휴머노이드 개발 착수 소식에 따른 긍정적 전망. 기술력에 대한 높은 평가와 함께 주가 상승에 대한 기대감이 나타남.</t>
+          <t>휴머노이드 개발 착수 및 NPU 기술력 기반, AI 반도체 파트너 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['휴머노이드', 'NPU', '기술력']</t>
+          <t>['NPU', '휴머노이드', 'AI']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5460811984</v>
+        <v>5462280449</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64700</v>
+        <v>64600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+23.71%</t>
+          <t>'+23.52%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>172621893100</v>
+        <v>174259373300</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13430</v>
+        <v>13720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+20.77%</t>
+          <t>'+23.38%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="F5" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="G5" t="n">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>253196201805</v>
+        <v>260386434100</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼미금속 주가 하락에 대한 부정적 전망과 경고. 일부 투자자들의 매수 행태를 이해하지 못하겠다는 의견과 함께 하한가 가능성을 언급.</t>
+          <t>단기 급등 후 하한가 가능성 언급, 수급 및 투매 물량 주의.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['하한가', '주가', '거래량']</t>
+          <t>['급등', '하한가', '수급']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111300</v>
+        <v>111000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.22%</t>
+          <t>'+8.93%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>304917227100</v>
+        <v>308664701800</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,27 +1027,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30950</v>
+        <v>31075</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.28%</t>
+          <t>'+7.71%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="H7" t="n">
-        <v>52.51</v>
+        <v>52.54</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>25.79</v>
       </c>
       <c r="O7" t="n">
-        <v>171083531025</v>
+        <v>177551712150</v>
       </c>
       <c r="P7" t="n">
         <v>31400</v>
@@ -1115,70 +1115,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31550</v>
+        <v>22950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.23%</t>
+          <t>'+6.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.62</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="H8" t="n">
-        <v>11.3</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29700</v>
+        <v>21500</v>
       </c>
       <c r="K8" t="n">
-        <v>30500</v>
+        <v>21200</v>
       </c>
       <c r="L8" t="n">
-        <v>33450</v>
+        <v>23400</v>
       </c>
       <c r="M8" t="n">
-        <v>30000</v>
+        <v>20850</v>
       </c>
       <c r="N8" t="n">
-        <v>11.92</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>266847445075</v>
+        <v>78214092975</v>
       </c>
       <c r="P8" t="n">
-        <v>75900</v>
+        <v>23400</v>
       </c>
       <c r="Q8" t="n">
-        <v>15000</v>
+        <v>9900</v>
       </c>
       <c r="R8" t="n">
-        <v>207000</v>
+        <v>79000</v>
       </c>
       <c r="S8" t="n">
-        <v>7000</v>
+        <v>-8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>단기 3만 5천원 가능성 언급. AI 전력수요 증가에 따른 기대감. 가온전선과의 비교 및 주가 부진에 대한 우려.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '전력수요', '거래량']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22600</v>
+        <v>31500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.12%</t>
+          <t>'+6.06%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2</v>
+        <v>11.3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>21500</v>
+        <v>29700</v>
       </c>
       <c r="K9" t="n">
-        <v>21200</v>
+        <v>30500</v>
       </c>
       <c r="L9" t="n">
-        <v>23200</v>
+        <v>33450</v>
       </c>
       <c r="M9" t="n">
-        <v>20850</v>
+        <v>30000</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>11.92</v>
       </c>
       <c r="O9" t="n">
-        <v>67850598475</v>
+        <v>269857852425</v>
       </c>
       <c r="P9" t="n">
-        <v>23200</v>
+        <v>75900</v>
       </c>
       <c r="Q9" t="n">
-        <v>9900</v>
+        <v>15000</v>
       </c>
       <c r="R9" t="n">
-        <v>79000</v>
+        <v>207000</v>
       </c>
       <c r="S9" t="n">
-        <v>-8000</v>
+        <v>7000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>단기 3만 5천원 가능성 언급. AI 전력수요 증가에 따른 기대감. 가온전선과의 비교 및 주가 부진에 대한 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['AI', '전력수요', '거래량']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18740</v>
+        <v>18730</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.41%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" t="n">
-        <v>746</v>
+        <v>765</v>
       </c>
       <c r="H10" t="n">
         <v>10.47</v>
@@ -1346,7 +1346,7 @@
         <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>152533381585</v>
+        <v>154984016565</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 관련 내용 언급 및 감사원 신고 완료 주장. 미국 증시 폭등과 함께 상승 기대.</t>
+          <t>감사원 신고 및 공매도 관련 의혹 제기, 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '감사원', '상승']</t>
+          <t>['감사원', '공매도', '시세조종']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.19</v>
       </c>
       <c r="E11" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0.19</v>
       </c>
       <c r="O11" t="n">
-        <v>68346548885</v>
+        <v>68748773415</v>
       </c>
       <c r="P11" t="n">
         <v>13140</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>211500</v>
+        <v>13120</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.68%</t>
+          <t>'+1.23%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>352</v>
+        <v>396</v>
       </c>
       <c r="H12" t="n">
-        <v>75.5</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>208000</v>
+        <v>12960</v>
       </c>
       <c r="K12" t="n">
-        <v>215000</v>
+        <v>13500</v>
       </c>
       <c r="L12" t="n">
-        <v>216000</v>
+        <v>14190</v>
       </c>
       <c r="M12" t="n">
-        <v>211000</v>
+        <v>13100</v>
       </c>
       <c r="N12" t="n">
-        <v>75.44</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>824691961000</v>
+        <v>22727819095</v>
       </c>
       <c r="P12" t="n">
-        <v>243500</v>
+        <v>19380</v>
       </c>
       <c r="Q12" t="n">
-        <v>64700</v>
+        <v>3200</v>
       </c>
       <c r="R12" t="n">
-        <v>-683000</v>
+        <v>-46000</v>
       </c>
       <c r="S12" t="n">
-        <v>-90000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13140</v>
+        <v>210500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.39%</t>
+          <t>'+1.20%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>75.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12960</v>
+        <v>208000</v>
       </c>
       <c r="K13" t="n">
-        <v>13500</v>
+        <v>215000</v>
       </c>
       <c r="L13" t="n">
-        <v>14190</v>
+        <v>216000</v>
       </c>
       <c r="M13" t="n">
-        <v>13120</v>
+        <v>210000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>75.44</v>
       </c>
       <c r="O13" t="n">
-        <v>22557596260</v>
+        <v>857883988750</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>243500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>64700</v>
       </c>
       <c r="R13" t="n">
-        <v>-46000</v>
+        <v>-683000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-90000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,222 +1660,222 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86200</v>
+        <v>6380</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.06%</t>
+          <t>'+1.11%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="E14" t="n">
-        <v>412</v>
+        <v>84</v>
       </c>
       <c r="F14" t="n">
-        <v>219</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>1501</v>
+        <v>187</v>
       </c>
       <c r="H14" t="n">
-        <v>23.05</v>
+        <v>4.86</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>85300</v>
+        <v>6310</v>
       </c>
       <c r="K14" t="n">
-        <v>87000</v>
+        <v>6460</v>
       </c>
       <c r="L14" t="n">
-        <v>88100</v>
+        <v>7090</v>
       </c>
       <c r="M14" t="n">
-        <v>85200</v>
+        <v>6330</v>
       </c>
       <c r="N14" t="n">
-        <v>23.12</v>
+        <v>4.95</v>
       </c>
       <c r="O14" t="n">
-        <v>214007176650</v>
+        <v>54181860260</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>11760</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>1620</v>
       </c>
       <c r="R14" t="n">
-        <v>-240000</v>
+        <v>-74000</v>
       </c>
       <c r="S14" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 대미 투자 및 SMR 추진 확정 소식으로 인한 긍정적 전망. 공급 계약 체결에 대한 축하 메시지와 함께 주가 상승 기대감 표출.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대미투자', 'SMR', '공급계약']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6370</v>
+        <v>86200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.95%</t>
+          <t>'+1.06%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>83</v>
+        <v>417</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c r="G15" t="n">
-        <v>187</v>
+        <v>1519</v>
       </c>
       <c r="H15" t="n">
-        <v>4.86</v>
+        <v>23.05</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6310</v>
+        <v>85300</v>
       </c>
       <c r="K15" t="n">
-        <v>6460</v>
+        <v>87000</v>
       </c>
       <c r="L15" t="n">
-        <v>7090</v>
+        <v>88100</v>
       </c>
       <c r="M15" t="n">
-        <v>6330</v>
+        <v>85200</v>
       </c>
       <c r="N15" t="n">
-        <v>4.95</v>
+        <v>23.12</v>
       </c>
       <c r="O15" t="n">
-        <v>54014395300</v>
+        <v>219091915050</v>
       </c>
       <c r="P15" t="n">
-        <v>11760</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>1620</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-74000</v>
+        <v>-240000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>두산에너빌리티의 대미 투자 및 SMR 추진 확정 소식으로 인한 긍정적 전망. 공급 계약 체결에 대한 축하 메시지와 함께 주가 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['대미투자', 'SMR', '공급계약']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>276000</v>
+        <v>320000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.73%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>137</v>
       </c>
       <c r="F16" t="n">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>1861</v>
+        <v>314</v>
       </c>
       <c r="H16" t="n">
-        <v>46.56</v>
+        <v>3.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>274000</v>
+        <v>318500</v>
       </c>
       <c r="K16" t="n">
-        <v>283000</v>
+        <v>333000</v>
       </c>
       <c r="L16" t="n">
-        <v>283500</v>
+        <v>349500</v>
       </c>
       <c r="M16" t="n">
-        <v>275500</v>
+        <v>319500</v>
       </c>
       <c r="N16" t="n">
-        <v>46.46</v>
+        <v>3.62</v>
       </c>
       <c r="O16" t="n">
-        <v>3557264373250</v>
+        <v>126059617000</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>635000</v>
       </c>
       <c r="Q16" t="n">
-        <v>81100</v>
+        <v>52600</v>
       </c>
       <c r="R16" t="n">
-        <v>550000</v>
+        <v>-7000</v>
       </c>
       <c r="S16" t="n">
-        <v>307000</v>
+        <v>5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>삼성전자에 대한 긍정적 기대감과 함께 주가 상승 전망 언급. 다만, 일부 부정적 의견과 함께 물량 출회에 대한 우려도 존재.</t>
+          <t>가온전선 주가 상승에 대한 긍정적 전망. 52주 신고가 돌파 기대감과 함께 40만원, 50만원 목표가를 제시하며 매수세를 독려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['특별배당', '실적', '주가']</t>
+          <t>['신고가', '목표가', '성장동력']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>320500</v>
+        <v>13600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.63%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.4</v>
+        <v>-0.34</v>
       </c>
       <c r="E17" t="n">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>312</v>
+        <v>222</v>
       </c>
       <c r="H17" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>318500</v>
+        <v>13540</v>
       </c>
       <c r="K17" t="n">
-        <v>333000</v>
+        <v>13870</v>
       </c>
       <c r="L17" t="n">
-        <v>349500</v>
+        <v>14650</v>
       </c>
       <c r="M17" t="n">
-        <v>320000</v>
+        <v>13570</v>
       </c>
       <c r="N17" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="O17" t="n">
-        <v>122914990500</v>
+        <v>98380484685</v>
       </c>
       <c r="P17" t="n">
-        <v>635000</v>
+        <v>20300</v>
       </c>
       <c r="Q17" t="n">
-        <v>52600</v>
+        <v>2885</v>
       </c>
       <c r="R17" t="n">
-        <v>-7000</v>
+        <v>8000</v>
       </c>
       <c r="S17" t="n">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>가온전선 주가 상승에 대한 긍정적 전망. 52주 신고가 돌파 기대감과 함께 40만원, 50만원 목표가를 제시하며 매수세를 독려.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['신고가', '목표가', '성장동력']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,82 +2023,82 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13600</v>
+        <v>13430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.34</v>
+        <v>-0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>217</v>
+        <v>566</v>
       </c>
       <c r="H18" t="n">
-        <v>3.34</v>
+        <v>5.02</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13540</v>
+        <v>13400</v>
       </c>
       <c r="K18" t="n">
-        <v>13870</v>
+        <v>13630</v>
       </c>
       <c r="L18" t="n">
-        <v>14650</v>
+        <v>13800</v>
       </c>
       <c r="M18" t="n">
-        <v>13590</v>
+        <v>13180</v>
       </c>
       <c r="N18" t="n">
-        <v>3.68</v>
+        <v>5.5</v>
       </c>
       <c r="O18" t="n">
-        <v>97589239195</v>
+        <v>67602062595</v>
       </c>
       <c r="P18" t="n">
-        <v>20300</v>
+        <v>30200</v>
       </c>
       <c r="Q18" t="n">
-        <v>2885</v>
+        <v>3540</v>
       </c>
       <c r="R18" t="n">
-        <v>8000</v>
+        <v>-91000</v>
       </c>
       <c r="S18" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 협상 등 긍정적 뉴스 기반. 주가 상승 기대감 및 추가 매수 권유.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['SMR', '웨스팅하우스', '원전']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,99 +2120,99 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13360</v>
+        <v>274500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.30%</t>
+          <t>'+0.18%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.48</v>
+        <v>0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>61</v>
+        <v>484</v>
       </c>
       <c r="G19" t="n">
-        <v>562</v>
+        <v>1838</v>
       </c>
       <c r="H19" t="n">
-        <v>5.02</v>
+        <v>46.56</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13400</v>
+        <v>274000</v>
       </c>
       <c r="K19" t="n">
-        <v>13630</v>
+        <v>283000</v>
       </c>
       <c r="L19" t="n">
-        <v>13800</v>
+        <v>283500</v>
       </c>
       <c r="M19" t="n">
-        <v>13180</v>
+        <v>274500</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5</v>
+        <v>46.46</v>
       </c>
       <c r="O19" t="n">
-        <v>66741781170</v>
+        <v>3789131680000</v>
       </c>
       <c r="P19" t="n">
-        <v>30200</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>3540</v>
+        <v>81100</v>
       </c>
       <c r="R19" t="n">
-        <v>-91000</v>
+        <v>550000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>307000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 협상 등 긍정적 뉴스 기반. 주가 상승 기대감 및 추가 매수 권유.</t>
+          <t>주가 30만원 및 내년 배당 10% 기대, 단 물량 지속 출회 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['SMR', '웨스팅하우스', '원전']</t>
+          <t>['배당', '실적', '물량']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8480</v>
+        <v>8470</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-0.59%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F20" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H20" t="n">
         <v>26.58</v>
@@ -2266,7 +2266,7 @@
         <v>26.57</v>
       </c>
       <c r="O20" t="n">
-        <v>20027455225</v>
+        <v>20301631735</v>
       </c>
       <c r="P20" t="n">
         <v>17950</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17620</v>
+        <v>17590</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'-0.73%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-1.68</v>
       </c>
       <c r="E21" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F21" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G21" t="n">
-        <v>799</v>
+        <v>810</v>
       </c>
       <c r="H21" t="n">
         <v>6.22</v>
@@ -2358,7 +2358,7 @@
         <v>7.9</v>
       </c>
       <c r="O21" t="n">
-        <v>161213216990</v>
+        <v>164618071860</v>
       </c>
       <c r="P21" t="n">
         <v>31500</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10480</v>
+        <v>10450</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.66%</t>
+          <t>'-0.95%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>42</v>
       </c>
       <c r="G22" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H22" t="n">
         <v>9.609999999999999</v>
@@ -2450,7 +2450,7 @@
         <v>8.6</v>
       </c>
       <c r="O22" t="n">
-        <v>142705857420</v>
+        <v>144519444080</v>
       </c>
       <c r="P22" t="n">
         <v>11640</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1849000</v>
+        <v>1834000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-1.02%</t>
+          <t>'-1.82%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="G23" t="n">
-        <v>1658</v>
+        <v>1626</v>
       </c>
       <c r="H23" t="n">
         <v>50.17</v>
@@ -2536,13 +2536,13 @@
         <v>1935000</v>
       </c>
       <c r="M23" t="n">
-        <v>1846000</v>
+        <v>1832000</v>
       </c>
       <c r="N23" t="n">
         <v>50.23</v>
       </c>
       <c r="O23" t="n">
-        <v>4372674227500</v>
+        <v>4591913145500</v>
       </c>
       <c r="P23" t="n">
         <v>2987000</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 하락에 대한 불만과 부정적 전망. 연기금 매도와 기관 수급에 대한 비판, 그리고 장중 주가 변동성에 대한 우려가 나타남.</t>
+          <t>주가 하락에 대한 불만 표출 및 기관 매도세 우려.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['연기금', '주가', '기관']</t>
+          <t>['하락', '연기금', '매도세']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2587,70 +2587,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23950</v>
+        <v>10225</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.15%</t>
+          <t>'-3.17%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.41</v>
+        <v>-0.4</v>
       </c>
       <c r="E24" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F24" t="n">
         <v>62</v>
       </c>
       <c r="G24" t="n">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="H24" t="n">
-        <v>1.76</v>
+        <v>17.89</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>25250</v>
+        <v>10560</v>
       </c>
       <c r="K24" t="n">
-        <v>26150</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>26600</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>23550</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.35</v>
+        <v>18.29</v>
       </c>
       <c r="O24" t="n">
-        <v>107906339825</v>
+        <v>41339000000</v>
       </c>
       <c r="P24" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>16000</v>
+        <v>-11000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>미국 임상 FDA 관련 기대감 있으나, 단기 변동성 및 재무 상태에 대한 우려.</t>
+          <t>투자경고 종목 지정 및 단주치기 등 거래 행태에 대한 부정적 인식. 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['FDA', '임상', '재무']</t>
+          <t>['투자경고', '단주치기', '주가']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,77 +2672,77 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10220</v>
+        <v>23950</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-7.59%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.4</v>
+        <v>1.41</v>
       </c>
       <c r="E25" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F25" t="n">
         <v>61</v>
       </c>
       <c r="G25" t="n">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="H25" t="n">
-        <v>17.89</v>
+        <v>1.76</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>11060</v>
+        <v>25250</v>
       </c>
       <c r="K25" t="n">
-        <v>10570</v>
+        <v>26150</v>
       </c>
       <c r="L25" t="n">
-        <v>10815</v>
+        <v>26600</v>
       </c>
       <c r="M25" t="n">
-        <v>10060</v>
+        <v>23550</v>
       </c>
       <c r="N25" t="n">
-        <v>18.29</v>
+        <v>0.35</v>
       </c>
       <c r="O25" t="n">
-        <v>41110837205</v>
+        <v>108562588975</v>
       </c>
       <c r="P25" t="n">
-        <v>22450</v>
+        <v>39350</v>
       </c>
       <c r="Q25" t="n">
-        <v>1760</v>
+        <v>8200</v>
       </c>
       <c r="R25" t="n">
-        <v>-11000</v>
+        <v>16000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 및 단주치기 등 거래 행태에 대한 부정적 인식. 주가 하락 우려.</t>
+          <t>미국 임상 FDA 관련 기대감 있으나, 단기 변동성 및 재무 상태에 대한 우려.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['투자경고', '단주치기', '주가']</t>
+          <t>['FDA', '임상', '재무']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3720</v>
+        <v>3730</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-8.26%</t>
+          <t>'-8.01%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.63</v>
       </c>
       <c r="E26" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F26" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G26" t="n">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="H26" t="n">
         <v>0.96</v>
@@ -2812,13 +2812,13 @@
         <v>4080</v>
       </c>
       <c r="M26" t="n">
-        <v>3720</v>
+        <v>3710</v>
       </c>
       <c r="N26" t="n">
         <v>0.33</v>
       </c>
       <c r="O26" t="n">
-        <v>12859656295</v>
+        <v>13102991840</v>
       </c>
       <c r="P26" t="n">
         <v>6480</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>텐베거 기대감 속 급락 및 신규 매수 개미 몰살 우려. 차트상 말아 올리는 패턴 기대.</t>
+          <t>코인 관련주, 단기 급락 후 반등 기대와 대규모 지옥 전망 공존.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['텐베거', '차트분석', '급락']</t>
+          <t>['코인', '급락', '반등']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">

--- a/data/trending_integrated_20260922_14.xlsx
+++ b/data/trending_integrated_20260922_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52415911440</v>
+        <v>52424728490</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5462280449</v>
+        <v>5476304434</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64600</v>
+        <v>13860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+23.52%</t>
+          <t>'+24.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="G4" t="n">
-        <v>162</v>
+        <v>513</v>
       </c>
       <c r="H4" t="n">
-        <v>6.87</v>
+        <v>0.62</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>52300</v>
+        <v>11120</v>
       </c>
       <c r="K4" t="n">
-        <v>60800</v>
+        <v>11270</v>
       </c>
       <c r="L4" t="n">
-        <v>67900</v>
+        <v>14140</v>
       </c>
       <c r="M4" t="n">
-        <v>59700</v>
+        <v>10810</v>
       </c>
       <c r="N4" t="n">
-        <v>6.88</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>174259373300</v>
+        <v>268472493060</v>
       </c>
       <c r="P4" t="n">
-        <v>148300</v>
+        <v>20850</v>
       </c>
       <c r="Q4" t="n">
-        <v>16300</v>
+        <v>4020</v>
       </c>
       <c r="R4" t="n">
-        <v>-15000</v>
+        <v>-39000</v>
       </c>
       <c r="S4" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>브로드컴 투자 공급 계약 뉴스 기반 상승 기대. 20일선 안착 여부 및 키 맞추기 가능성 언급.</t>
+          <t>단기 급등 후 하한가 가능성 언급, 수급 및 투매 물량 주의.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공급계약', '20일선', '키맞추기']</t>
+          <t>['급등', '하한가', '수급']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,91 +827,91 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13720</v>
+        <v>65100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+23.38%</t>
+          <t>'+24.47%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>211</v>
+        <v>113</v>
       </c>
       <c r="F5" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="G5" t="n">
-        <v>496</v>
+        <v>163</v>
       </c>
       <c r="H5" t="n">
-        <v>0.62</v>
+        <v>6.87</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11120</v>
+        <v>52300</v>
       </c>
       <c r="K5" t="n">
-        <v>11270</v>
+        <v>60800</v>
       </c>
       <c r="L5" t="n">
-        <v>14140</v>
+        <v>67900</v>
       </c>
       <c r="M5" t="n">
-        <v>10810</v>
+        <v>59700</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7</v>
+        <v>6.88</v>
       </c>
       <c r="O5" t="n">
-        <v>260386434100</v>
+        <v>175673860400</v>
       </c>
       <c r="P5" t="n">
-        <v>20850</v>
+        <v>148300</v>
       </c>
       <c r="Q5" t="n">
-        <v>4020</v>
+        <v>16300</v>
       </c>
       <c r="R5" t="n">
-        <v>-24000</v>
+        <v>3000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>단기 급등 후 하한가 가능성 언급, 수급 및 투매 물량 주의.</t>
+          <t>브로드컴 투자 공급 계약 뉴스 기반 상승 기대. 20일선 안착 여부 및 키 맞추기 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['급등', '하한가', '수급']</t>
+          <t>['공급계약', '20일선', '키맞추기']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,12 +919,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111000</v>
+        <v>111600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.93%</t>
+          <t>'+9.52%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
         <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>308664701800</v>
+        <v>311786506200</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -987,10 +987,10 @@
         <v>26350</v>
       </c>
       <c r="R6" t="n">
-        <v>234000</v>
+        <v>269000</v>
       </c>
       <c r="S6" t="n">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1027,27 +1027,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31075</v>
+        <v>31100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.71%</t>
+          <t>'+7.80%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="H7" t="n">
-        <v>52.54</v>
+        <v>52.56</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>25.79</v>
       </c>
       <c r="O7" t="n">
-        <v>177551712150</v>
+        <v>180107808475</v>
       </c>
       <c r="P7" t="n">
         <v>31400</v>
@@ -1079,10 +1079,10 @@
         <v>21000</v>
       </c>
       <c r="R7" t="n">
-        <v>872000</v>
+        <v>1391000</v>
       </c>
       <c r="S7" t="n">
-        <v>265000</v>
+        <v>323000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1115,70 +1115,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22950</v>
+        <v>31700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.74%</t>
+          <t>'+6.73%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>-0.62</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="G8" t="n">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>11.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>21500</v>
+        <v>29700</v>
       </c>
       <c r="K8" t="n">
-        <v>21200</v>
+        <v>30500</v>
       </c>
       <c r="L8" t="n">
-        <v>23400</v>
+        <v>33450</v>
       </c>
       <c r="M8" t="n">
-        <v>20850</v>
+        <v>30000</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>11.92</v>
       </c>
       <c r="O8" t="n">
-        <v>78214092975</v>
+        <v>272003444700</v>
       </c>
       <c r="P8" t="n">
-        <v>23400</v>
+        <v>75900</v>
       </c>
       <c r="Q8" t="n">
-        <v>9900</v>
+        <v>15000</v>
       </c>
       <c r="R8" t="n">
-        <v>79000</v>
+        <v>753000</v>
       </c>
       <c r="S8" t="n">
-        <v>-8000</v>
+        <v>14000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>단기 3만 5천원 가능성 언급. AI 전력수요 증가에 따른 기대감. 가온전선과의 비교 및 주가 부진에 대한 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['AI', '전력수요', '거래량']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31500</v>
+        <v>22500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.06%</t>
+          <t>'+4.65%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.62</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="H9" t="n">
-        <v>11.3</v>
+        <v>1.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>29700</v>
+        <v>21500</v>
       </c>
       <c r="K9" t="n">
-        <v>30500</v>
+        <v>21200</v>
       </c>
       <c r="L9" t="n">
-        <v>33450</v>
+        <v>23400</v>
       </c>
       <c r="M9" t="n">
-        <v>30000</v>
+        <v>20850</v>
       </c>
       <c r="N9" t="n">
-        <v>11.92</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>269857852425</v>
+        <v>83765300000</v>
       </c>
       <c r="P9" t="n">
-        <v>75900</v>
+        <v>23400</v>
       </c>
       <c r="Q9" t="n">
-        <v>15000</v>
+        <v>9900</v>
       </c>
       <c r="R9" t="n">
-        <v>207000</v>
+        <v>-43000</v>
       </c>
       <c r="S9" t="n">
-        <v>7000</v>
+        <v>-8000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 3만 5천원 가능성 언급. AI 전력수요 증가에 따른 기대감. 가온전선과의 비교 및 주가 부진에 대한 우려.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '전력수요', '거래량']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18730</v>
+        <v>18880</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.41%</t>
+          <t>'+3.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>85</v>
       </c>
       <c r="G10" t="n">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="H10" t="n">
         <v>10.47</v>
@@ -1346,7 +1346,7 @@
         <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>154984016565</v>
+        <v>156830316740</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1355,23 +1355,23 @@
         <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>146000</v>
+        <v>388000</v>
       </c>
       <c r="S10" t="n">
-        <v>41000</v>
+        <v>96000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>감사원 신고 및 공매도 관련 의혹 제기, 주가 상승 기대.</t>
+          <t>대우건설, 감사원 신고 완료 및 공매도 세력 견제 움직임. 미국 증시 폭등과 LNG 기대감에 따른 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['감사원', '공매도', '시세조종']</t>
+          <t>['공매도', '감사원', 'LNG']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5970</v>
+        <v>5990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.88%</t>
+          <t>'+2.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.19</v>
       </c>
       <c r="E11" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0.19</v>
       </c>
       <c r="O11" t="n">
-        <v>68748773415</v>
+        <v>68906472245</v>
       </c>
       <c r="P11" t="n">
         <v>13140</v>
@@ -1447,10 +1447,10 @@
         <v>3725</v>
       </c>
       <c r="R11" t="n">
-        <v>-259000</v>
+        <v>-237000</v>
       </c>
       <c r="S11" t="n">
-        <v>34000</v>
+        <v>38000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13120</v>
+        <v>324500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'+1.88%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="E12" t="n">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="G12" t="n">
-        <v>396</v>
+        <v>315</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>12960</v>
+        <v>318500</v>
       </c>
       <c r="K12" t="n">
-        <v>13500</v>
+        <v>333000</v>
       </c>
       <c r="L12" t="n">
-        <v>14190</v>
+        <v>349500</v>
       </c>
       <c r="M12" t="n">
-        <v>13100</v>
+        <v>319000</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O12" t="n">
-        <v>22727819095</v>
+        <v>128218395000</v>
       </c>
       <c r="P12" t="n">
-        <v>19380</v>
+        <v>635000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3200</v>
+        <v>52600</v>
       </c>
       <c r="R12" t="n">
-        <v>-46000</v>
+        <v>-8000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>가온전선 주가 상승에 대한 긍정적 전망. 52주 신고가 돌파 기대감과 함께 40만원, 50만원 목표가를 제시하며 매수세를 독려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['신고가', '목표가', '성장동력']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>210500</v>
+        <v>13200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.20%</t>
+          <t>'+1.85%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="H13" t="n">
-        <v>75.5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>208000</v>
+        <v>12960</v>
       </c>
       <c r="K13" t="n">
-        <v>215000</v>
+        <v>13500</v>
       </c>
       <c r="L13" t="n">
-        <v>216000</v>
+        <v>14190</v>
       </c>
       <c r="M13" t="n">
-        <v>210000</v>
+        <v>13100</v>
       </c>
       <c r="N13" t="n">
-        <v>75.44</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>857883988750</v>
+        <v>23110839795</v>
       </c>
       <c r="P13" t="n">
-        <v>243500</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>64700</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-683000</v>
+        <v>-49000</v>
       </c>
       <c r="S13" t="n">
-        <v>-90000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6380</v>
+        <v>6420</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.11%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H14" t="n">
         <v>4.86</v>
@@ -1714,7 +1714,7 @@
         <v>4.95</v>
       </c>
       <c r="O14" t="n">
-        <v>54181860260</v>
+        <v>54385895800</v>
       </c>
       <c r="P14" t="n">
         <v>11760</v>
@@ -1723,7 +1723,7 @@
         <v>1620</v>
       </c>
       <c r="R14" t="n">
-        <v>-74000</v>
+        <v>-112000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86200</v>
+        <v>86600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.06%</t>
+          <t>'+1.52%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F15" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G15" t="n">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="H15" t="n">
         <v>23.05</v>
@@ -1806,7 +1806,7 @@
         <v>23.12</v>
       </c>
       <c r="O15" t="n">
-        <v>219091915050</v>
+        <v>222202818100</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1815,23 +1815,23 @@
         <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-240000</v>
+        <v>-253000</v>
       </c>
       <c r="S15" t="n">
-        <v>-8000</v>
+        <v>7000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 대미 투자 및 SMR 추진 확정 소식으로 인한 긍정적 전망. 공급 계약 체결에 대한 축하 메시지와 함께 주가 상승 기대감 표출.</t>
+          <t>두산에너빌리티, 미국 SMR 투자 확정 및 공급 계약 체결 소식. 대미 투자 관련 긍정적 전망으로 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대미투자', 'SMR', '공급계약']</t>
+          <t>['SMR', '대미투자', '공급계약']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>320000</v>
+        <v>211000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+1.44%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.4</v>
+        <v>0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="F16" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="H16" t="n">
-        <v>3.22</v>
+        <v>75.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>318500</v>
+        <v>208000</v>
       </c>
       <c r="K16" t="n">
-        <v>333000</v>
+        <v>215000</v>
       </c>
       <c r="L16" t="n">
-        <v>349500</v>
+        <v>216000</v>
       </c>
       <c r="M16" t="n">
-        <v>319500</v>
+        <v>210000</v>
       </c>
       <c r="N16" t="n">
-        <v>3.62</v>
+        <v>75.44</v>
       </c>
       <c r="O16" t="n">
-        <v>126059617000</v>
+        <v>891650701000</v>
       </c>
       <c r="P16" t="n">
-        <v>635000</v>
+        <v>243500</v>
       </c>
       <c r="Q16" t="n">
-        <v>52600</v>
+        <v>64700</v>
       </c>
       <c r="R16" t="n">
-        <v>-7000</v>
+        <v>-699000</v>
       </c>
       <c r="S16" t="n">
-        <v>5000</v>
+        <v>-168000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>가온전선 주가 상승에 대한 긍정적 전망. 52주 신고가 돌파 기대감과 함께 40만원, 50만원 목표가를 제시하며 매수세를 독려.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['신고가', '목표가', '성장동력']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13600</v>
+        <v>13670</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+0.96%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.34</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n">
         <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H17" t="n">
         <v>3.34</v>
@@ -1990,7 +1990,7 @@
         <v>3.68</v>
       </c>
       <c r="O17" t="n">
-        <v>98380484685</v>
+        <v>98808551515</v>
       </c>
       <c r="P17" t="n">
         <v>20300</v>
@@ -1999,10 +1999,10 @@
         <v>2885</v>
       </c>
       <c r="R17" t="n">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="S17" t="n">
-        <v>13000</v>
+        <v>16000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2035,307 +2035,307 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13430</v>
+        <v>276500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+0.91%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.48</v>
+        <v>0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>96</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>481</v>
       </c>
       <c r="G18" t="n">
-        <v>566</v>
+        <v>1750</v>
       </c>
       <c r="H18" t="n">
-        <v>5.02</v>
+        <v>46.56</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13400</v>
+        <v>274000</v>
       </c>
       <c r="K18" t="n">
-        <v>13630</v>
+        <v>283000</v>
       </c>
       <c r="L18" t="n">
-        <v>13800</v>
+        <v>283500</v>
       </c>
       <c r="M18" t="n">
-        <v>13180</v>
+        <v>274500</v>
       </c>
       <c r="N18" t="n">
-        <v>5.5</v>
+        <v>46.46</v>
       </c>
       <c r="O18" t="n">
-        <v>67602062595</v>
+        <v>3954065789000</v>
       </c>
       <c r="P18" t="n">
-        <v>30200</v>
+        <v>374500</v>
       </c>
       <c r="Q18" t="n">
-        <v>3540</v>
+        <v>81100</v>
       </c>
       <c r="R18" t="n">
-        <v>-91000</v>
+        <v>749000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>262000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 협상 등 긍정적 뉴스 기반. 주가 상승 기대감 및 추가 매수 권유.</t>
+          <t>삼성전자, 한국 신뢰도 급상승 및 주가 상승 기대감 언급. 특별 배당 권리 확보 및 3분기 실적 이슈 예상.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SMR', '웨스팅하우스', '원전']</t>
+          <t>['특별배당', '실적', '주가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>274500</v>
+        <v>13500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.18%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1</v>
+        <v>-0.48</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>484</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>1838</v>
+        <v>569</v>
       </c>
       <c r="H19" t="n">
-        <v>46.56</v>
+        <v>5.02</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>274000</v>
+        <v>13400</v>
       </c>
       <c r="K19" t="n">
-        <v>283000</v>
+        <v>13630</v>
       </c>
       <c r="L19" t="n">
-        <v>283500</v>
+        <v>13800</v>
       </c>
       <c r="M19" t="n">
-        <v>274500</v>
+        <v>13180</v>
       </c>
       <c r="N19" t="n">
-        <v>46.46</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3789131680000</v>
+        <v>68522711285</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>30200</v>
       </c>
       <c r="Q19" t="n">
-        <v>81100</v>
+        <v>3540</v>
       </c>
       <c r="R19" t="n">
-        <v>550000</v>
+        <v>-173000</v>
       </c>
       <c r="S19" t="n">
-        <v>307000</v>
+        <v>21000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 30만원 및 내년 배당 10% 기대, 단 물량 지속 출회 우려.</t>
+          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 협상 등 긍정적 뉴스 기반. 주가 상승 기대감 및 추가 매수 권유.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['배당', '실적', '물량']</t>
+          <t>['SMR', '웨스팅하우스', '원전']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8470</v>
+        <v>17740</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'+0.11%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="G20" t="n">
-        <v>399</v>
+        <v>825</v>
       </c>
       <c r="H20" t="n">
-        <v>26.58</v>
+        <v>6.22</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8520</v>
+        <v>17720</v>
       </c>
       <c r="K20" t="n">
-        <v>8620</v>
+        <v>18230</v>
       </c>
       <c r="L20" t="n">
-        <v>8650</v>
+        <v>18750</v>
       </c>
       <c r="M20" t="n">
-        <v>8410</v>
+        <v>17500</v>
       </c>
       <c r="N20" t="n">
-        <v>26.57</v>
+        <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>20301631735</v>
+        <v>166639231500</v>
       </c>
       <c r="P20" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>8120</v>
+        <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>-436000</v>
+        <v>-475000</v>
       </c>
       <c r="S20" t="n">
-        <v>72000</v>
+        <v>14000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>대미 투자 관련 언급이 다수 확인되며, SMR 추진 및 가스터빈 기술에 대한 기대감 존재. 주가 상승에 대한 기대와 우려가 공존.</t>
+          <t>대한광통신, 미국 광통신주 강세에 따른 동반 상승 기대. 공매도 수량 부족 언급 및 추세 변함없음 주장.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['SMR', '대미 투자', '가스터빈']</t>
+          <t>['광케이블', '공매도', '실적주']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17590</v>
+        <v>10560</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.73%</t>
+          <t>'+0.09%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.68</v>
+        <v>1.01</v>
       </c>
       <c r="E21" t="n">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>810</v>
+        <v>196</v>
       </c>
       <c r="H21" t="n">
-        <v>6.22</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,130 +2343,130 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17720</v>
+        <v>10550</v>
       </c>
       <c r="K21" t="n">
-        <v>18230</v>
+        <v>10730</v>
       </c>
       <c r="L21" t="n">
-        <v>18750</v>
+        <v>11160</v>
       </c>
       <c r="M21" t="n">
-        <v>17500</v>
+        <v>10300</v>
       </c>
       <c r="N21" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="O21" t="n">
-        <v>164618071860</v>
+        <v>146364106330</v>
       </c>
       <c r="P21" t="n">
-        <v>31500</v>
+        <v>11640</v>
       </c>
       <c r="Q21" t="n">
-        <v>1272</v>
+        <v>3735</v>
       </c>
       <c r="R21" t="n">
-        <v>-494000</v>
+        <v>326000</v>
       </c>
       <c r="S21" t="n">
-        <v>14000</v>
+        <v>-790000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대감. 실적 및 추세 긍정적 전망.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['광통신', '실적', '추세']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10450</v>
+        <v>8470</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.95%</t>
+          <t>'-0.59%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.01</v>
+        <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>196</v>
+        <v>409</v>
       </c>
       <c r="H22" t="n">
-        <v>9.609999999999999</v>
+        <v>26.58</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10550</v>
+        <v>8520</v>
       </c>
       <c r="K22" t="n">
-        <v>10730</v>
+        <v>8620</v>
       </c>
       <c r="L22" t="n">
-        <v>11160</v>
+        <v>8650</v>
       </c>
       <c r="M22" t="n">
-        <v>10300</v>
+        <v>8410</v>
       </c>
       <c r="N22" t="n">
-        <v>8.6</v>
+        <v>26.57</v>
       </c>
       <c r="O22" t="n">
-        <v>144519444080</v>
+        <v>21201770615</v>
       </c>
       <c r="P22" t="n">
-        <v>11640</v>
+        <v>17950</v>
       </c>
       <c r="Q22" t="n">
-        <v>3735</v>
+        <v>8120</v>
       </c>
       <c r="R22" t="n">
-        <v>215000</v>
+        <v>-498000</v>
       </c>
       <c r="S22" t="n">
-        <v>-478000</v>
+        <v>47000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>대미 투자 관련 언급이 다수 확인되며, SMR 추진 및 가스터빈 기술에 대한 기대감 존재. 주가 상승에 대한 기대와 우려가 공존.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['SMR', '대미 투자', '가스터빈']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1834000</v>
+        <v>1844000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-1.82%</t>
+          <t>'-1.28%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G23" t="n">
-        <v>1626</v>
+        <v>1489</v>
       </c>
       <c r="H23" t="n">
         <v>50.17</v>
@@ -2542,7 +2542,7 @@
         <v>50.23</v>
       </c>
       <c r="O23" t="n">
-        <v>4591913145500</v>
+        <v>4776129594500</v>
       </c>
       <c r="P23" t="n">
         <v>2987000</v>
@@ -2551,23 +2551,23 @@
         <v>333000</v>
       </c>
       <c r="R23" t="n">
-        <v>44000</v>
+        <v>-27000</v>
       </c>
       <c r="S23" t="n">
-        <v>31000</v>
+        <v>14000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 불만 표출 및 기관 매도세 우려.</t>
+          <t>SK하이닉스, 국내 증시 하락 및 연기금 매도에 대한 불만 표출. 주가 하락 속도에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['하락', '연기금', '매도세']</t>
+          <t>['연기금', '주가하락', '반도체']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2587,70 +2587,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10225</v>
+        <v>23950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-3.17%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.4</v>
+        <v>1.41</v>
       </c>
       <c r="E24" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G24" t="n">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="H24" t="n">
-        <v>17.89</v>
+        <v>1.76</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>10560</v>
+        <v>25250</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>26150</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>26600</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>23550</v>
       </c>
       <c r="N24" t="n">
-        <v>18.29</v>
+        <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>41339000000</v>
+        <v>109091216825</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>39350</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="R24" t="n">
-        <v>-11000</v>
+        <v>2000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 및 단주치기 등 거래 행태에 대한 부정적 인식. 주가 하락 우려.</t>
+          <t>미국 임상 FDA 관련 기대감 있으나, 단기 변동성 및 재무 상태에 대한 우려.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['투자경고', '단주치기', '주가']</t>
+          <t>['FDA', '임상', '재무']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,77 +2672,77 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>23950</v>
+        <v>10260</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-5.15%</t>
+          <t>'-7.23%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.41</v>
+        <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F25" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G25" t="n">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="H25" t="n">
-        <v>1.76</v>
+        <v>17.89</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>25250</v>
+        <v>11060</v>
       </c>
       <c r="K25" t="n">
-        <v>26150</v>
+        <v>10570</v>
       </c>
       <c r="L25" t="n">
-        <v>26600</v>
+        <v>10815</v>
       </c>
       <c r="M25" t="n">
-        <v>23550</v>
+        <v>10060</v>
       </c>
       <c r="N25" t="n">
-        <v>0.35</v>
+        <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>108562588975</v>
+        <v>41596805530</v>
       </c>
       <c r="P25" t="n">
-        <v>39350</v>
+        <v>22450</v>
       </c>
       <c r="Q25" t="n">
-        <v>8200</v>
+        <v>1760</v>
       </c>
       <c r="R25" t="n">
-        <v>16000</v>
+        <v>-11000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>미국 임상 FDA 관련 기대감 있으나, 단기 변동성 및 재무 상태에 대한 우려.</t>
+          <t>투자경고 종목 지정 및 단주치기 등 거래 행태에 대한 부정적 인식. 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['FDA', '임상', '재무']</t>
+          <t>['투자경고', '단주치기', '주가']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3730</v>
+        <v>3735</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-8.01%</t>
+          <t>'-7.89%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.63</v>
       </c>
       <c r="E26" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F26" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G26" t="n">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="H26" t="n">
         <v>0.96</v>
@@ -2818,7 +2818,7 @@
         <v>0.33</v>
       </c>
       <c r="O26" t="n">
-        <v>13102991840</v>
+        <v>13296692250</v>
       </c>
       <c r="P26" t="n">
         <v>6480</v>
@@ -2827,10 +2827,10 @@
         <v>1738</v>
       </c>
       <c r="R26" t="n">
-        <v>-28000</v>
+        <v>-78000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/data/trending_integrated_20260922_14.xlsx
+++ b/data/trending_integrated_20260922_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F2" t="n">
         <v>94</v>
       </c>
       <c r="G2" t="n">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52424728490</v>
+        <v>52589997440</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>휴머노이드 개발 착수 및 NPU 기술력 기반, AI 반도체 파트너 기대.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 및 기술력 부각. 7배 초가속, 3배 작업 속도 향상 등 메가톤급 재료 언급. 빅테크 기업의 인수 가능성 시사.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', 'AI']</t>
+          <t>['NPU', '휴머노이드', 'AI반도체']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -676,7 +676,7 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5476304434</v>
+        <v>5476405409</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13860</v>
+        <v>65400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+24.64%</t>
+          <t>'+25.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="F4" t="n">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>513</v>
+        <v>165</v>
       </c>
       <c r="H4" t="n">
-        <v>0.62</v>
+        <v>6.87</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11120</v>
+        <v>52300</v>
       </c>
       <c r="K4" t="n">
-        <v>11270</v>
+        <v>60800</v>
       </c>
       <c r="L4" t="n">
-        <v>14140</v>
+        <v>67900</v>
       </c>
       <c r="M4" t="n">
-        <v>10810</v>
+        <v>59700</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>268472493060</v>
+        <v>176977383900</v>
       </c>
       <c r="P4" t="n">
-        <v>20850</v>
+        <v>148300</v>
       </c>
       <c r="Q4" t="n">
-        <v>4020</v>
+        <v>16300</v>
       </c>
       <c r="R4" t="n">
-        <v>-39000</v>
+        <v>3000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>단기 급등 후 하한가 가능성 언급, 수급 및 투매 물량 주의.</t>
+          <t>브로드컴 투자 공급 계약 뉴스 기반 상승 기대. 20일선 안착 여부 및 키 맞추기 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['급등', '하한가', '수급']</t>
+          <t>['공급계약', '20일선', '키맞추기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,91 +827,91 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65100</v>
+        <v>13570</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+24.47%</t>
+          <t>'+22.03%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>113</v>
+        <v>224</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="G5" t="n">
-        <v>163</v>
+        <v>554</v>
       </c>
       <c r="H5" t="n">
-        <v>6.87</v>
+        <v>0.62</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>52300</v>
+        <v>11120</v>
       </c>
       <c r="K5" t="n">
-        <v>60800</v>
+        <v>11270</v>
       </c>
       <c r="L5" t="n">
-        <v>67900</v>
+        <v>14140</v>
       </c>
       <c r="M5" t="n">
-        <v>59700</v>
+        <v>10810</v>
       </c>
       <c r="N5" t="n">
-        <v>6.88</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>175673860400</v>
+        <v>273615833680</v>
       </c>
       <c r="P5" t="n">
-        <v>148300</v>
+        <v>20850</v>
       </c>
       <c r="Q5" t="n">
-        <v>16300</v>
+        <v>4020</v>
       </c>
       <c r="R5" t="n">
-        <v>3000</v>
+        <v>-39000</v>
       </c>
       <c r="S5" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>브로드컴 투자 공급 계약 뉴스 기반 상승 기대. 20일선 안착 여부 및 키 맞추기 가능성 언급.</t>
+          <t>급등 후 하한가 논란 속에서 매수/매도세 공방. 단기보다 장기 투자를 강조하는 의견과 사기꾼, 개잡주라는 비난.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['공급계약', '20일선', '키맞추기']</t>
+          <t>['급등', '하한가', '수급']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,12 +919,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111600</v>
+        <v>112400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.52%</t>
+          <t>'+10.30%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>311786506200</v>
+        <v>314268451100</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,27 +1027,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31100</v>
+        <v>31200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.80%</t>
+          <t>'+8.15%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" t="n">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="H7" t="n">
-        <v>52.56</v>
+        <v>52.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>25.79</v>
       </c>
       <c r="O7" t="n">
-        <v>180107808475</v>
+        <v>185126038850</v>
       </c>
       <c r="P7" t="n">
         <v>31400</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31700</v>
+        <v>31850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.73%</t>
+          <t>'+7.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>82</v>
       </c>
       <c r="G8" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H8" t="n">
         <v>11.3</v>
@@ -1162,7 +1162,7 @@
         <v>11.92</v>
       </c>
       <c r="O8" t="n">
-        <v>272003444700</v>
+        <v>274324583525</v>
       </c>
       <c r="P8" t="n">
         <v>75900</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22500</v>
+        <v>22600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.65%</t>
+          <t>'+5.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
         <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="H9" t="n">
         <v>1.2</v>
@@ -1254,7 +1254,7 @@
         <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>83765300000</v>
+        <v>86050768475</v>
       </c>
       <c r="P9" t="n">
         <v>23400</v>
@@ -1303,18 +1303,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18880</v>
+        <v>18870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.23%</t>
+          <t>'+3.17%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F10" t="n">
         <v>85</v>
@@ -1346,7 +1346,7 @@
         <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>156830316740</v>
+        <v>158587384095</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대우건설, 감사원 신고 완료 및 공매도 세력 견제 움직임. 미국 증시 폭등과 LNG 기대감에 따른 주가 상승 전망.</t>
+          <t>공매도 세력과의 싸움 속에서 2만 돌파 및 상한가 기대감 형성. 감사원 신고 완료 및 공매도 장부 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '감사원', 'LNG']</t>
+          <t>['공매도', '상한가', '감사원']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5990</v>
+        <v>212500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.22%</t>
+          <t>'+2.16%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>171</v>
+        <v>360</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>75.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5860</v>
+        <v>208000</v>
       </c>
       <c r="K11" t="n">
-        <v>6200</v>
+        <v>215000</v>
       </c>
       <c r="L11" t="n">
-        <v>6610</v>
+        <v>216000</v>
       </c>
       <c r="M11" t="n">
-        <v>5950</v>
+        <v>210000</v>
       </c>
       <c r="N11" t="n">
-        <v>0.19</v>
+        <v>75.44</v>
       </c>
       <c r="O11" t="n">
-        <v>68906472245</v>
+        <v>920116808250</v>
       </c>
       <c r="P11" t="n">
-        <v>13140</v>
+        <v>243500</v>
       </c>
       <c r="Q11" t="n">
-        <v>3725</v>
+        <v>64700</v>
       </c>
       <c r="R11" t="n">
-        <v>-237000</v>
+        <v>-699000</v>
       </c>
       <c r="S11" t="n">
-        <v>38000</v>
+        <v>-168000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>비트코인 급등에 따른 가상화폐 테마 상승 기대감. 업비트 상장 및 공매도 관련 언급.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['비트코인', '가상화폐', '공매도']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,86 +1476,86 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>324500</v>
+        <v>6440</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.88%</t>
+          <t>'+2.06%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.4</v>
+        <v>-0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="F12" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>315</v>
+        <v>190</v>
       </c>
       <c r="H12" t="n">
-        <v>3.22</v>
+        <v>4.86</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>318500</v>
+        <v>6310</v>
       </c>
       <c r="K12" t="n">
-        <v>333000</v>
+        <v>6460</v>
       </c>
       <c r="L12" t="n">
-        <v>349500</v>
+        <v>7090</v>
       </c>
       <c r="M12" t="n">
-        <v>319000</v>
+        <v>6330</v>
       </c>
       <c r="N12" t="n">
-        <v>3.62</v>
+        <v>4.95</v>
       </c>
       <c r="O12" t="n">
-        <v>128218395000</v>
+        <v>54646092865</v>
       </c>
       <c r="P12" t="n">
-        <v>635000</v>
+        <v>11760</v>
       </c>
       <c r="Q12" t="n">
-        <v>52600</v>
+        <v>1620</v>
       </c>
       <c r="R12" t="n">
-        <v>-8000</v>
+        <v>-112000</v>
       </c>
       <c r="S12" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>가온전선 주가 상승에 대한 긍정적 전망. 52주 신고가 돌파 기대감과 함께 40만원, 50만원 목표가를 제시하며 매수세를 독려.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신고가', '목표가', '성장동력']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,82 +1563,82 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13200</v>
+        <v>5980</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.85%</t>
+          <t>'+2.05%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="E13" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>401</v>
+        <v>176</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12960</v>
+        <v>5860</v>
       </c>
       <c r="K13" t="n">
-        <v>13500</v>
+        <v>6200</v>
       </c>
       <c r="L13" t="n">
-        <v>14190</v>
+        <v>6610</v>
       </c>
       <c r="M13" t="n">
-        <v>13100</v>
+        <v>5950</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="O13" t="n">
-        <v>23110839795</v>
+        <v>69196784210</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>13140</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>3725</v>
       </c>
       <c r="R13" t="n">
-        <v>-49000</v>
+        <v>-237000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>비트코인 급등에 따른 가상화폐 테마 상승 기대감. 업비트 상장 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['비트코인', '가상화폐', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6420</v>
+        <v>324500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+1.88%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.09</v>
+        <v>-0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>189</v>
+        <v>319</v>
       </c>
       <c r="H14" t="n">
-        <v>4.86</v>
+        <v>3.22</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6310</v>
+        <v>318500</v>
       </c>
       <c r="K14" t="n">
-        <v>6460</v>
+        <v>333000</v>
       </c>
       <c r="L14" t="n">
-        <v>7090</v>
+        <v>349500</v>
       </c>
       <c r="M14" t="n">
-        <v>6330</v>
+        <v>319000</v>
       </c>
       <c r="N14" t="n">
-        <v>4.95</v>
+        <v>3.62</v>
       </c>
       <c r="O14" t="n">
-        <v>54385895800</v>
+        <v>129470364000</v>
       </c>
       <c r="P14" t="n">
-        <v>11760</v>
+        <v>635000</v>
       </c>
       <c r="Q14" t="n">
-        <v>1620</v>
+        <v>52600</v>
       </c>
       <c r="R14" t="n">
-        <v>-112000</v>
+        <v>-8000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>52주 신고가 돌파 및 40만원, 50만원 목표 제시. 구리 가격 상승 및 발전 프로젝트 테마 언급. 야수의 심장으로 덤빌 구간 진입.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['신고가', '테마주', '목표가']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,43 +1747,43 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86600</v>
+        <v>13190</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.52%</t>
+          <t>'+1.77%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="F15" t="n">
-        <v>221</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>1523</v>
+        <v>401</v>
       </c>
       <c r="H15" t="n">
-        <v>23.05</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>85300</v>
+        <v>12960</v>
       </c>
       <c r="K15" t="n">
-        <v>87000</v>
+        <v>13500</v>
       </c>
       <c r="L15" t="n">
-        <v>88100</v>
+        <v>14190</v>
       </c>
       <c r="M15" t="n">
-        <v>85200</v>
+        <v>13100</v>
       </c>
       <c r="N15" t="n">
-        <v>23.12</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>222202818100</v>
+        <v>23262214880</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>-253000</v>
+        <v>-49000</v>
       </c>
       <c r="S15" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 미국 SMR 투자 확정 및 공급 계약 체결 소식. 대미 투자 관련 긍정적 전망으로 주가 상승 기대.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['SMR', '대미투자', '공급계약']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>211000</v>
+        <v>86800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.44%</t>
+          <t>'+1.76%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>78</v>
+        <v>427</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>222</v>
       </c>
       <c r="G16" t="n">
-        <v>348</v>
+        <v>1557</v>
       </c>
       <c r="H16" t="n">
-        <v>75.5</v>
+        <v>23.05</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>208000</v>
+        <v>85300</v>
       </c>
       <c r="K16" t="n">
-        <v>215000</v>
+        <v>87000</v>
       </c>
       <c r="L16" t="n">
-        <v>216000</v>
+        <v>88100</v>
       </c>
       <c r="M16" t="n">
-        <v>210000</v>
+        <v>85200</v>
       </c>
       <c r="N16" t="n">
-        <v>75.44</v>
+        <v>23.12</v>
       </c>
       <c r="O16" t="n">
-        <v>891650701000</v>
+        <v>226779199300</v>
       </c>
       <c r="P16" t="n">
-        <v>243500</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>64700</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>-699000</v>
+        <v>-253000</v>
       </c>
       <c r="S16" t="n">
-        <v>-168000</v>
+        <v>7000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>두산에너빌리티, 미국 SMR 투자 확정 및 공급 계약 체결 소식. 대미 투자 관련 긍정적 전망으로 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['SMR', '대미투자', '공급계약']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13670</v>
+        <v>277750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+1.37%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.34</v>
+        <v>0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>48</v>
+        <v>487</v>
       </c>
       <c r="G17" t="n">
-        <v>226</v>
+        <v>1764</v>
       </c>
       <c r="H17" t="n">
-        <v>3.34</v>
+        <v>46.56</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,222 +1975,222 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13540</v>
+        <v>274000</v>
       </c>
       <c r="K17" t="n">
-        <v>13870</v>
+        <v>283000</v>
       </c>
       <c r="L17" t="n">
-        <v>14650</v>
+        <v>283500</v>
       </c>
       <c r="M17" t="n">
-        <v>13570</v>
+        <v>274500</v>
       </c>
       <c r="N17" t="n">
-        <v>3.68</v>
+        <v>46.46</v>
       </c>
       <c r="O17" t="n">
-        <v>98808551515</v>
+        <v>4083871760750</v>
       </c>
       <c r="P17" t="n">
-        <v>20300</v>
+        <v>374500</v>
       </c>
       <c r="Q17" t="n">
-        <v>2885</v>
+        <v>81100</v>
       </c>
       <c r="R17" t="n">
-        <v>2000</v>
+        <v>749000</v>
       </c>
       <c r="S17" t="n">
-        <v>16000</v>
+        <v>262000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>주가 30만원 기대감 속 배당락 및 3분기 실적 이슈 논의. 정치적 발언과 함께 일부 투자자들의 차익 실현 움직임.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['배당', '실적', '주가']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>276500</v>
+        <v>13520</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.91%</t>
+          <t>'+0.90%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1</v>
+        <v>-0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>97</v>
       </c>
       <c r="F18" t="n">
-        <v>481</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>1750</v>
+        <v>580</v>
       </c>
       <c r="H18" t="n">
-        <v>46.56</v>
+        <v>5.02</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>274000</v>
+        <v>13400</v>
       </c>
       <c r="K18" t="n">
-        <v>283000</v>
+        <v>13630</v>
       </c>
       <c r="L18" t="n">
-        <v>283500</v>
+        <v>13800</v>
       </c>
       <c r="M18" t="n">
-        <v>274500</v>
+        <v>13180</v>
       </c>
       <c r="N18" t="n">
-        <v>46.46</v>
+        <v>5.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3954065789000</v>
+        <v>69142224185</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>30200</v>
       </c>
       <c r="Q18" t="n">
-        <v>81100</v>
+        <v>3540</v>
       </c>
       <c r="R18" t="n">
-        <v>749000</v>
+        <v>-173000</v>
       </c>
       <c r="S18" t="n">
-        <v>262000</v>
+        <v>21000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>삼성전자, 한국 신뢰도 급상승 및 주가 상승 기대감 언급. 특별 배당 권리 확보 및 3분기 실적 이슈 예상.</t>
+          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 협상 등 긍정적 뉴스 기반. 주가 상승 기대감 및 추가 매수 권유.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['특별배당', '실적', '주가']</t>
+          <t>['SMR', '웨스팅하우스', '원전']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13500</v>
+        <v>13660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.75%</t>
+          <t>'+0.89%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.48</v>
+        <v>-0.34</v>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F19" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>569</v>
+        <v>230</v>
       </c>
       <c r="H19" t="n">
-        <v>5.02</v>
+        <v>3.34</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13400</v>
+        <v>13540</v>
       </c>
       <c r="K19" t="n">
-        <v>13630</v>
+        <v>13870</v>
       </c>
       <c r="L19" t="n">
-        <v>13800</v>
+        <v>14650</v>
       </c>
       <c r="M19" t="n">
-        <v>13180</v>
+        <v>13570</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5</v>
+        <v>3.68</v>
       </c>
       <c r="O19" t="n">
-        <v>68522711285</v>
+        <v>99204635490</v>
       </c>
       <c r="P19" t="n">
-        <v>30200</v>
+        <v>20300</v>
       </c>
       <c r="Q19" t="n">
-        <v>3540</v>
+        <v>2885</v>
       </c>
       <c r="R19" t="n">
-        <v>-173000</v>
+        <v>2000</v>
       </c>
       <c r="S19" t="n">
-        <v>21000</v>
+        <v>16000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 협상 등 긍정적 뉴스 기반. 주가 상승 기대감 및 추가 매수 권유.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['SMR', '웨스팅하우스', '원전']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17740</v>
+        <v>17770</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.11%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F20" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G20" t="n">
-        <v>825</v>
+        <v>841</v>
       </c>
       <c r="H20" t="n">
         <v>6.22</v>
@@ -2266,7 +2266,7 @@
         <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>166639231500</v>
+        <v>168585062910</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10560</v>
+        <v>10570</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.09%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>68</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H21" t="n">
         <v>9.609999999999999</v>
@@ -2358,7 +2358,7 @@
         <v>8.6</v>
       </c>
       <c r="O21" t="n">
-        <v>146364106330</v>
+        <v>148465157260</v>
       </c>
       <c r="P21" t="n">
         <v>11640</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8470</v>
+        <v>8480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F22" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H22" t="n">
         <v>26.58</v>
@@ -2450,7 +2450,7 @@
         <v>26.57</v>
       </c>
       <c r="O22" t="n">
-        <v>21201770615</v>
+        <v>21525560855</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>대미 투자 관련 언급이 다수 확인되며, SMR 추진 및 가스터빈 기술에 대한 기대감 존재. 주가 상승에 대한 기대와 우려가 공존.</t>
+          <t>주가 부진에 대한 답답함과 기대감 혼재. ADR 계산법 및 기관 순매수 동향 언급. 최악의 회사라는 평가도.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['SMR', '대미 투자', '가스터빈']</t>
+          <t>['주가', 'ADR', '기관']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1844000</v>
+        <v>1856000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'-0.64%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="G23" t="n">
-        <v>1489</v>
+        <v>1420</v>
       </c>
       <c r="H23" t="n">
         <v>50.17</v>
@@ -2542,7 +2542,7 @@
         <v>50.23</v>
       </c>
       <c r="O23" t="n">
-        <v>4776129594500</v>
+        <v>4942001618500</v>
       </c>
       <c r="P23" t="n">
         <v>2987000</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>SK하이닉스, 국내 증시 하락 및 연기금 매도에 대한 불만 표출. 주가 하락 속도에 대한 부정적 인식.</t>
+          <t>급격한 하락세에 대한 불만과 투자 포기 심리 확산. 연기금 매도세 및 해외 증시 영향에 대한 우려.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['연기금', '주가하락', '반도체']</t>
+          <t>['하락', '연기금', '외인']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23950</v>
+        <v>24150</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.15%</t>
+          <t>'-4.36%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1.41</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F24" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G24" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="H24" t="n">
         <v>1.76</v>
@@ -2634,7 +2634,7 @@
         <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>109091216825</v>
+        <v>109856633850</v>
       </c>
       <c r="P24" t="n">
         <v>39350</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10260</v>
+        <v>10270</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-7.23%</t>
+          <t>'-7.14%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F25" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G25" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H25" t="n">
         <v>17.89</v>
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>41596805530</v>
+        <v>41875737925</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3735</v>
+        <v>3745</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-7.89%</t>
+          <t>'-7.64%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.63</v>
       </c>
       <c r="E26" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F26" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G26" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H26" t="n">
         <v>0.96</v>
@@ -2818,7 +2818,7 @@
         <v>0.33</v>
       </c>
       <c r="O26" t="n">
-        <v>13296692250</v>
+        <v>13602315205</v>
       </c>
       <c r="P26" t="n">
         <v>6480</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>코인 관련주, 단기 급락 후 반등 기대와 대규모 지옥 전망 공존.</t>
+          <t>급락 후 반등 기대감과 폭락 우려 공존. 코인주 텐베거 가능성 및 차트 분석 언급. 선수 퇴장 및 개미 몰살 중.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['코인', '급락', '반등']</t>
+          <t>['코인주', '차트', '급락']</t>
         </is>
       </c>
       <c r="X26" t="n">
